--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -537,14 +537,14 @@
         <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>0.732</v>
+        <v>0.722</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>34-11</t>
+          <t>34-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
         <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>0.662</v>
+        <v>0.667</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -629,16 +629,16 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -754,14 +754,14 @@
         <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.625</v>
+        <v>0.616</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>29-17</t>
+          <t>29-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -893,17 +893,17 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
         <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>0.556</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22-21</t>
+          <t>23-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -918,11 +918,11 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>118</v>
       </c>
       <c r="P7" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
@@ -964,17 +964,17 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
         <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>0.542</v>
+        <v>0.548</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>22-23</t>
+          <t>23-23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -984,16 +984,16 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="M8" t="n">
         <v>8.5</v>
@@ -1005,10 +1005,10 @@
         <v>116</v>
       </c>
       <c r="P8" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>7</v>
@@ -1017,11 +1017,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1035,36 +1035,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F9" t="n">
         <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>23-20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
@@ -1073,13 +1073,13 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P9" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>8</v>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1159,11 +1159,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1187,41 +1187,41 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>22-20</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P11" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="M12" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1322,14 +1322,14 @@
         <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-28</t>
+          <t>17-29</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1360,7 +1360,7 @@
         <v>116</v>
       </c>
       <c r="P13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q13" t="n">
         <v>-4</v>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="M14" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="M15" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
@@ -1543,10 +1543,10 @@
         <v>16</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1618,10 +1618,10 @@
         <v>57</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.792</v>
+        <v>0.781</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10-0</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 12</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1656,7 +1656,7 @@
         <v>119</v>
       </c>
       <c r="P17" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q17" t="n">
         <v>11</v>
@@ -1690,22 +1690,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.75</v>
+        <v>0.753</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>31-14</t>
+          <t>32-14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11-3</t>
+          <t>12-3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1715,11 +1715,11 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>W 6</t>
+          <t>W 7</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1731,7 +1731,7 @@
         <v>119</v>
       </c>
       <c r="P18" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q18" t="n">
         <v>8</v>
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F19" t="n">
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.639</v>
+        <v>0.644</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1790,11 +1790,11 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1803,13 +1803,13 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P19" t="n">
         <v>115</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
         <v>3</v>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="N20" t="n">
         <v>2</v>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="M21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="N21" t="n">
         <v>3</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="N22" t="n">
         <v>2</v>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="M23" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="M25" t="n">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="M26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="M27" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
@@ -2411,19 +2411,19 @@
         <v>24</v>
       </c>
       <c r="F28" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G28" t="n">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>19-27</t>
+          <t>19-28</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6-7</t>
+          <t>6-8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2433,14 +2433,14 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>32.5</v>
       </c>
       <c r="M28" t="n">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -2457,7 +2457,11 @@
       <c r="R28" t="n">
         <v>12</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - o</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2508,10 +2512,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="M29" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
@@ -2583,10 +2587,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="M30" t="n">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
@@ -2658,10 +2662,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>38.5</v>
+        <v>38</v>
       </c>
       <c r="M31" t="n">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2815,13 +2819,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.662</v>
+        <v>0.667</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2835,16 +2839,16 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2915,10 +2919,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -2986,10 +2990,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -3028,17 +3032,17 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.542</v>
+        <v>0.548</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22-23</t>
+          <t>23-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3048,16 +3052,16 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="M5" t="n">
         <v>8.5</v>
@@ -3069,10 +3073,10 @@
         <v>116</v>
       </c>
       <c r="P5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
@@ -3128,10 +3132,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="M6" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -3177,14 +3181,14 @@
         <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0.732</v>
+        <v>0.722</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>34-11</t>
+          <t>34-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3199,7 +3203,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -3252,14 +3256,14 @@
         <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.625</v>
+        <v>0.616</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>29-17</t>
+          <t>29-18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3269,12 +3273,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -3349,10 +3353,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="M9" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -3394,14 +3398,14 @@
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-28</t>
+          <t>17-29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3416,7 +3420,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -3432,7 +3436,7 @@
         <v>116</v>
       </c>
       <c r="P10" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q10" t="n">
         <v>-4</v>
@@ -3465,10 +3469,10 @@
         <v>16</v>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -3487,7 +3491,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -3540,10 +3544,10 @@
         <v>57</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.792</v>
+        <v>0.781</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3557,12 +3561,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10-0</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>W 12</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -3578,7 +3582,7 @@
         <v>119</v>
       </c>
       <c r="P12" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
@@ -3641,10 +3645,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -3712,10 +3716,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="M14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
@@ -3783,10 +3787,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="M15" t="n">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
@@ -3854,10 +3858,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="M16" t="n">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -3900,13 +3904,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" t="n">
         <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>0.639</v>
+        <v>0.644</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3925,11 +3929,11 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -3938,13 +3942,13 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P17" t="n">
         <v>115</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
         <v>3</v>
@@ -4000,10 +4004,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="M18" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -4071,10 +4075,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -4142,10 +4146,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="N20" t="n">
         <v>4</v>
@@ -4213,10 +4217,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>38.5</v>
+        <v>38</v>
       </c>
       <c r="M21" t="n">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4259,17 +4263,17 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F22" t="n">
         <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>0.556</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>22-21</t>
+          <t>23-21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4284,11 +4288,11 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4300,7 +4304,7 @@
         <v>118</v>
       </c>
       <c r="P22" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -4312,11 +4316,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4330,36 +4334,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F23" t="n">
         <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>23-20</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="M23" t="n">
         <v>2</v>
@@ -4368,13 +4372,13 @@
         <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P23" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
         <v>8</v>
@@ -4430,10 +4434,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -4454,11 +4458,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4482,41 +4486,41 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22-20</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P25" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>
@@ -4572,10 +4576,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="M26" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -4618,22 +4622,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F27" t="n">
         <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>0.75</v>
+        <v>0.753</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>31-14</t>
+          <t>32-14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11-3</t>
+          <t>12-3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4643,11 +4647,11 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>W 6</t>
+          <t>W 7</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4659,7 +4663,7 @@
         <v>119</v>
       </c>
       <c r="P27" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q27" t="n">
         <v>8</v>
@@ -4722,10 +4726,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
@@ -4793,10 +4797,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="M29" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
@@ -4842,19 +4846,19 @@
         <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G30" t="n">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19-27</t>
+          <t>19-28</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6-7</t>
+          <t>6-8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4864,14 +4868,14 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>32.5</v>
       </c>
       <c r="M30" t="n">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -4888,7 +4892,11 @@
       <c r="R30" t="n">
         <v>12</v>
       </c>
-      <c r="S30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - o</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4939,10 +4947,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="M31" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -804,11 +804,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -818,52 +818,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>29-16</t>
+          <t>23-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L6" t="n">
         <v>11.5</v>
       </c>
       <c r="M6" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="P6" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Q6" t="n">
         <v>2</v>
@@ -875,11 +875,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -889,52 +889,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
         <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23-21</t>
+          <t>29-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P7" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
@@ -1251,10 +1251,10 @@
         <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1268,19 +1268,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="M12" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1289,7 +1289,7 @@
         <v>111</v>
       </c>
       <c r="P12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q12" t="n">
         <v>-6</v>
@@ -1372,11 +1372,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1400,41 +1400,41 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12-32</t>
+          <t>11-34</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>2-12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L 8</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>35</v>
       </c>
       <c r="M14" t="n">
-        <v>31</v>
+        <v>23.5</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P14" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="R14" t="n">
         <v>13</v>
@@ -1447,11 +1447,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1461,55 +1461,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>0.225</v>
+        <v>0.233</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11-34</t>
+          <t>12-32</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>3-12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L 16</t>
+          <t>L 9</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>35.5</v>
       </c>
       <c r="M15" t="n">
-        <v>24</v>
+        <v>31.5</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="P15" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="Q15" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="R15" t="n">
         <v>14</v>
@@ -1836,17 +1836,17 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F20" t="n">
         <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>0.616</v>
+        <v>0.622</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>27-16</t>
+          <t>28-16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1856,19 +1856,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N20" t="n">
         <v>2</v>
@@ -1877,7 +1877,7 @@
         <v>121</v>
       </c>
       <c r="P20" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q20" t="n">
         <v>4</v>
@@ -1907,17 +1907,17 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F21" t="n">
         <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>0.611</v>
+        <v>0.616</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27-21</t>
+          <t>28-21</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1932,14 +1932,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="N21" t="n">
         <v>3</v>
@@ -1948,7 +1948,7 @@
         <v>118</v>
       </c>
       <c r="P21" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
@@ -1981,14 +1981,14 @@
         <v>43</v>
       </c>
       <c r="F22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.606</v>
+        <v>0.597</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23-21</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1998,19 +1998,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="N22" t="n">
         <v>2</v>
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24" t="n">
         <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2145,14 +2145,14 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="M24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -2161,7 +2161,7 @@
         <v>114</v>
       </c>
       <c r="P24" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F25" t="n">
         <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2211,31 +2211,31 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="M25" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P25" t="n">
         <v>117</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R25" t="n">
         <v>9</v>
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
         <v>38</v>
       </c>
       <c r="G26" t="n">
-        <v>0.472</v>
+        <v>0.479</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2282,19 +2282,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="M26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
@@ -2486,14 +2486,14 @@
         <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G29" t="n">
-        <v>0.319</v>
+        <v>0.315</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12-32</t>
+          <t>12-33</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2508,14 +2508,14 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="M29" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
@@ -2561,10 +2561,10 @@
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G30" t="n">
-        <v>0.292</v>
+        <v>0.288</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2578,19 +2578,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="M30" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
@@ -2964,10 +2964,10 @@
         <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2986,14 +2986,14 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -3008,7 +3008,7 @@
         <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S4" t="inlineStr"/>
     </row>
@@ -3106,10 +3106,10 @@
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>0.236</v>
+        <v>0.233</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3123,19 +3123,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L 8</t>
+          <t>L 9</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="M6" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -3150,7 +3150,7 @@
         <v>-9</v>
       </c>
       <c r="R6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -3327,10 +3327,10 @@
         <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3344,19 +3344,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="M9" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -3365,7 +3365,7 @@
         <v>111</v>
       </c>
       <c r="P9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q9" t="n">
         <v>-6</v>
@@ -3616,17 +3616,17 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.616</v>
+        <v>0.622</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>27-16</t>
+          <t>28-16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3636,19 +3636,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -3657,7 +3657,7 @@
         <v>121</v>
       </c>
       <c r="P13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q13" t="n">
         <v>4</v>
@@ -3687,17 +3687,17 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
         <v>28</v>
       </c>
       <c r="G14" t="n">
-        <v>0.611</v>
+        <v>0.616</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27-21</t>
+          <t>28-21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3712,14 +3712,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
@@ -3728,7 +3728,7 @@
         <v>118</v>
       </c>
       <c r="P14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q14" t="n">
         <v>4</v>
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
         <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3778,31 +3778,31 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="M15" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P15" t="n">
         <v>117</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R15" t="n">
         <v>9</v>
@@ -3832,10 +3832,10 @@
         <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>0.292</v>
+        <v>0.288</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -3849,19 +3849,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="M16" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
         <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -4071,14 +4071,14 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -4087,7 +4087,7 @@
         <v>114</v>
       </c>
       <c r="P19" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -4117,13 +4117,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F20" t="n">
         <v>38</v>
       </c>
       <c r="G20" t="n">
-        <v>0.472</v>
+        <v>0.479</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="M20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="N20" t="n">
         <v>4</v>
@@ -4310,7 +4310,7 @@
         <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S22" t="inlineStr"/>
     </row>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F26" t="n">
         <v>55</v>
       </c>
       <c r="G26" t="n">
-        <v>0.225</v>
+        <v>0.236</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4567,19 +4567,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 16</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>35.5</v>
+        <v>35</v>
       </c>
       <c r="M26" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -4591,10 +4591,10 @@
         <v>124</v>
       </c>
       <c r="Q26" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="R26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -4700,14 +4700,14 @@
         <v>43</v>
       </c>
       <c r="F28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.606</v>
+        <v>0.597</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>23-21</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4717,19 +4717,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
@@ -4921,14 +4921,14 @@
         <v>23</v>
       </c>
       <c r="F31" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>0.319</v>
+        <v>0.315</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12-32</t>
+          <t>12-33</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4943,14 +4943,14 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="M31" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
         <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>0.722</v>
+        <v>0.726</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,12 +554,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P2" t="n">
         <v>110</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -683,14 +683,14 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>0.658</v>
+        <v>0.649</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>31-15</t>
+          <t>31-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -700,19 +700,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 7</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -721,7 +721,7 @@
         <v>117</v>
       </c>
       <c r="P4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q4" t="n">
         <v>7</v>
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M7" t="n">
         <v>8</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="M8" t="n">
         <v>8.5</v>
@@ -1017,11 +1017,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>23-20</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
@@ -1073,13 +1073,13 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P9" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>8</v>
@@ -1106,17 +1106,17 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F10" t="n">
         <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22-22</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1131,14 +1131,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L10" t="n">
         <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1159,11 +1159,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1177,51 +1177,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F11" t="n">
         <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>23-20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L11" t="n">
         <v>14</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P11" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="M12" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="M13" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="M14" t="n">
         <v>23.5</v>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="M15" t="n">
         <v>31.5</v>
@@ -1569,10 +1569,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M16" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -2336,10 +2336,10 @@
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G27" t="n">
-        <v>0.342</v>
+        <v>0.338</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2353,19 +2353,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="M27" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
@@ -2636,10 +2636,10 @@
         <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G31" t="n">
-        <v>0.26</v>
+        <v>0.257</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2658,14 +2658,14 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="M31" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2893,14 +2893,14 @@
         <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>0.658</v>
+        <v>0.649</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31-15</t>
+          <t>31-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2910,19 +2910,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 7</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -2931,7 +2931,7 @@
         <v>117</v>
       </c>
       <c r="P3" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q3" t="n">
         <v>7</v>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M4" t="n">
         <v>8</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="M5" t="n">
         <v>8.5</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="M6" t="n">
         <v>31.5</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0.722</v>
+        <v>0.726</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -3216,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P7" t="n">
         <v>110</v>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="M9" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="M10" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -4191,10 +4191,10 @@
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G21" t="n">
-        <v>0.26</v>
+        <v>0.257</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4213,14 +4213,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="M21" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4316,11 +4316,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23-20</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="M23" t="n">
         <v>2</v>
@@ -4372,13 +4372,13 @@
         <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P23" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>8</v>
@@ -4405,17 +4405,17 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
         <v>34</v>
       </c>
       <c r="G24" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>22-22</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -4430,14 +4430,14 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>14</v>
       </c>
       <c r="M24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -4458,11 +4458,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4476,51 +4476,51 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F25" t="n">
         <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>23-20</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>14</v>
       </c>
       <c r="M25" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P25" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="M26" t="n">
         <v>23.5</v>
@@ -4771,10 +4771,10 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G29" t="n">
-        <v>0.342</v>
+        <v>0.338</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -4788,19 +4788,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="M29" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
         <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>0.667</v>
+        <v>0.671</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>29-14</t>
+          <t>30-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -712,7 +712,7 @@
         <v>5.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -751,17 +751,17 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.616</v>
+        <v>0.622</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>29-18</t>
+          <t>30-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -771,19 +771,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M5" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
@@ -804,11 +804,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -818,52 +818,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23-21</t>
+          <t>29-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P6" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="Q6" t="n">
         <v>2</v>
@@ -875,11 +875,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -889,31 +889,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>0.556</v>
+        <v>0.554</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>29-16</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -925,16 +925,16 @@
         <v>12.5</v>
       </c>
       <c r="M7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="P7" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
@@ -996,7 +996,7 @@
         <v>13</v>
       </c>
       <c r="M8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
@@ -1017,11 +1017,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1045,29 +1045,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L9" t="n">
         <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1076,10 +1076,10 @@
         <v>116</v>
       </c>
       <c r="P9" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
         <v>8</v>
@@ -1088,11 +1088,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1116,29 +1116,29 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L10" t="n">
         <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1147,10 +1147,10 @@
         <v>116</v>
       </c>
       <c r="P10" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>9</v>
@@ -1180,14 +1180,14 @@
         <v>39</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>0.534</v>
+        <v>0.527</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>23-20</t>
+          <t>23-21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1197,16 +1197,16 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="M11" t="n">
         <v>2</v>
@@ -1218,7 +1218,7 @@
         <v>120</v>
       </c>
       <c r="P11" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q11" t="n">
         <v>3</v>
@@ -1322,10 +1322,10 @@
         <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>0.403</v>
+        <v>0.397</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1339,19 +1339,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="M13" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -1363,12 +1363,16 @@
         <v>121</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R13" t="n">
         <v>12</v>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - o</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1422,7 +1426,7 @@
         <v>35.5</v>
       </c>
       <c r="M14" t="n">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
@@ -1497,7 +1501,7 @@
         <v>36</v>
       </c>
       <c r="M15" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
@@ -1543,10 +1547,10 @@
         <v>16</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>0.219</v>
+        <v>0.216</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1565,14 +1569,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M16" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -1615,13 +1619,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.781</v>
+        <v>0.784</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1640,7 +1644,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1719,7 +1723,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1794,7 +1798,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1865,10 +1869,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N20" t="n">
         <v>2</v>
@@ -1936,10 +1940,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="N21" t="n">
         <v>3</v>
@@ -1978,39 +1982,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
         <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.597</v>
+        <v>0.603</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>24-22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7-6</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L22" t="n">
         <v>13.5</v>
       </c>
       <c r="M22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="N22" t="n">
         <v>2</v>
@@ -2078,7 +2082,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="M23" t="n">
         <v>7</v>
@@ -2120,13 +2124,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" t="n">
         <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.507</v>
+        <v>0.514</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2145,14 +2149,14 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>20</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -2161,7 +2165,7 @@
         <v>114</v>
       </c>
       <c r="P24" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
@@ -2220,10 +2224,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="M25" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
@@ -2291,7 +2295,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="M26" t="n">
         <v>12</v>
@@ -2362,7 +2366,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="M27" t="n">
         <v>30.5</v>
@@ -2411,19 +2415,19 @@
         <v>24</v>
       </c>
       <c r="F28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G28" t="n">
-        <v>0.333</v>
+        <v>0.329</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>19-28</t>
+          <t>19-29</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2433,14 +2437,14 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="M28" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -2512,7 +2516,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="M29" t="n">
         <v>32</v>
@@ -2587,10 +2591,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="M30" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
@@ -2662,7 +2666,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="M31" t="n">
         <v>28.5</v>
@@ -2819,17 +2823,17 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.667</v>
+        <v>0.671</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29-14</t>
+          <t>30-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2844,11 +2848,11 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2922,7 +2926,7 @@
         <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -2993,7 +2997,7 @@
         <v>12.5</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -3008,7 +3012,7 @@
         <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S4" t="inlineStr"/>
     </row>
@@ -3064,7 +3068,7 @@
         <v>13</v>
       </c>
       <c r="M5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -3135,7 +3139,7 @@
         <v>36</v>
       </c>
       <c r="M6" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -3253,17 +3257,17 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
         <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.616</v>
+        <v>0.622</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>29-18</t>
+          <t>30-18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3273,19 +3277,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -3398,10 +3402,10 @@
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>0.403</v>
+        <v>0.397</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3415,19 +3419,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="M10" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -3439,12 +3443,16 @@
         <v>121</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R10" t="n">
         <v>12</v>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - o</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3469,10 +3477,10 @@
         <v>16</v>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>0.219</v>
+        <v>0.216</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -3491,14 +3499,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M11" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -3541,13 +3549,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" t="n">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.781</v>
+        <v>0.784</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3566,7 +3574,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -3645,10 +3653,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -3716,10 +3724,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
@@ -3787,10 +3795,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="M15" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
@@ -3858,10 +3866,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="M16" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -3933,7 +3941,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -4004,7 +4012,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="M18" t="n">
         <v>7</v>
@@ -4046,13 +4054,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F19" t="n">
         <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>0.507</v>
+        <v>0.514</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -4071,14 +4079,14 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -4087,7 +4095,7 @@
         <v>114</v>
       </c>
       <c r="P19" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -4146,7 +4154,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="M20" t="n">
         <v>12</v>
@@ -4217,7 +4225,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="M21" t="n">
         <v>28.5</v>
@@ -4266,14 +4274,14 @@
         <v>41</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23-21</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4283,16 +4291,16 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4304,23 +4312,23 @@
         <v>118</v>
       </c>
       <c r="P22" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4344,29 +4352,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -4375,10 +4383,10 @@
         <v>116</v>
       </c>
       <c r="P23" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
         <v>8</v>
@@ -4387,11 +4395,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4415,29 +4423,29 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>14</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -4446,10 +4454,10 @@
         <v>116</v>
       </c>
       <c r="P24" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>9</v>
@@ -4479,14 +4487,14 @@
         <v>39</v>
       </c>
       <c r="F25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G25" t="n">
-        <v>0.534</v>
+        <v>0.527</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-20</t>
+          <t>23-21</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4496,16 +4504,16 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="M25" t="n">
         <v>2</v>
@@ -4517,7 +4525,7 @@
         <v>120</v>
       </c>
       <c r="P25" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
@@ -4579,7 +4587,7 @@
         <v>35.5</v>
       </c>
       <c r="M26" t="n">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -4651,7 +4659,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4697,39 +4705,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F28" t="n">
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.597</v>
+        <v>0.603</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>24-22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7-6</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>13.5</v>
       </c>
       <c r="M28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
@@ -4797,7 +4805,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="M29" t="n">
         <v>30.5</v>
@@ -4846,19 +4854,19 @@
         <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G30" t="n">
-        <v>0.333</v>
+        <v>0.329</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19-28</t>
+          <t>19-29</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4868,14 +4876,14 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="M30" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -4947,7 +4955,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="M31" t="n">
         <v>32</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.556</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -847,14 +847,14 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -1397,10 +1397,10 @@
         <v>17</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>0.236</v>
+        <v>0.233</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1419,14 +1419,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="M14" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
@@ -1472,10 +1472,10 @@
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>0.233</v>
+        <v>0.23</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1489,19 +1489,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L 9</t>
+          <t>L 10</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="M15" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F19" t="n">
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.644</v>
+        <v>0.649</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1794,11 +1794,11 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1840,39 +1840,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="n">
         <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>0.622</v>
+        <v>0.627</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>28-16</t>
+          <t>29-16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7-5</t>
+          <t>8-5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N20" t="n">
         <v>2</v>
@@ -2085,7 +2085,7 @@
         <v>17.5</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -2156,7 +2156,7 @@
         <v>20</v>
       </c>
       <c r="M24" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -2198,14 +2198,14 @@
         <v>37</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.493</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25-20</t>
+          <t>25-21</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2215,25 +2215,25 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="M25" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P25" t="n">
         <v>117</v>
@@ -2266,13 +2266,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F26" t="n">
         <v>38</v>
       </c>
       <c r="G26" t="n">
-        <v>0.479</v>
+        <v>0.486</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2286,16 +2286,16 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="M26" t="n">
         <v>12</v>
@@ -2340,10 +2340,10 @@
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2362,14 +2362,14 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="M27" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
@@ -2487,17 +2487,17 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
         <v>50</v>
       </c>
       <c r="G29" t="n">
-        <v>0.315</v>
+        <v>0.324</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12-33</t>
+          <t>13-33</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2507,19 +2507,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>34.5</v>
+        <v>34</v>
       </c>
       <c r="M29" t="n">
-        <v>32</v>
+        <v>31.5</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
@@ -2565,19 +2565,19 @@
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G30" t="n">
-        <v>0.288</v>
+        <v>0.284</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11-33</t>
+          <t>11-34</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>1-13</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2587,20 +2587,20 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M30" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P30" t="n">
         <v>125</v>
@@ -2669,7 +2669,7 @@
         <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>28.5</v>
+        <v>29</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>0.556</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2990,14 +2990,14 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -3110,10 +3110,10 @@
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>0.233</v>
+        <v>0.23</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3127,19 +3127,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L 9</t>
+          <t>L 10</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -3624,39 +3624,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.622</v>
+        <v>0.627</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28-16</t>
+          <t>29-16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7-5</t>
+          <t>8-5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -3769,14 +3769,14 @@
         <v>37</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.493</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>25-20</t>
+          <t>25-21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3786,25 +3786,25 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="M15" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P15" t="n">
         <v>117</v>
@@ -3840,19 +3840,19 @@
         <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>0.288</v>
+        <v>0.284</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-33</t>
+          <t>11-34</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>1-13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3862,20 +3862,20 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M16" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P16" t="n">
         <v>125</v>
@@ -3912,13 +3912,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" t="n">
         <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>0.644</v>
+        <v>0.649</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3937,11 +3937,11 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>17.5</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -4086,7 +4086,7 @@
         <v>20</v>
       </c>
       <c r="M19" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -4125,13 +4125,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
         <v>38</v>
       </c>
       <c r="G20" t="n">
-        <v>0.479</v>
+        <v>0.486</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4145,16 +4145,16 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="M20" t="n">
         <v>12</v>
@@ -4228,7 +4228,7 @@
         <v>39</v>
       </c>
       <c r="M21" t="n">
-        <v>28.5</v>
+        <v>29</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4558,10 +4558,10 @@
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G26" t="n">
-        <v>0.236</v>
+        <v>0.233</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4580,14 +4580,14 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -4779,10 +4779,10 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G29" t="n">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="M29" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
@@ -4926,17 +4926,17 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31" t="n">
         <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>0.315</v>
+        <v>0.324</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12-33</t>
+          <t>13-33</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4946,19 +4946,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>34.5</v>
+        <v>34</v>
       </c>
       <c r="M31" t="n">
-        <v>32</v>
+        <v>31.5</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
         <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>0.726</v>
+        <v>0.73</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -575,7 +575,7 @@
         <v>118</v>
       </c>
       <c r="P2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q2" t="n">
         <v>8</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>1.5</v>
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M6" t="n">
         <v>8</v>
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
         <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>0.554</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -964,17 +964,17 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
         <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>0.548</v>
+        <v>0.554</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>23-23</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -984,19 +984,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>13</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
@@ -1005,7 +1005,7 @@
         <v>116</v>
       </c>
       <c r="P8" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1017,11 +1017,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1045,29 +1045,29 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1076,10 +1076,10 @@
         <v>116</v>
       </c>
       <c r="P9" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>8</v>
@@ -1088,11 +1088,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1109,19 +1109,19 @@
         <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>0.534</v>
+        <v>0.527</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>23-21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1131,26 +1131,26 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P10" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
         <v>9</v>
@@ -1159,11 +1159,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1187,17 +1187,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>23-21</t>
+          <t>23-23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1206,22 +1206,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P11" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
@@ -1251,10 +1251,10 @@
         <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>0.403</v>
+        <v>0.397</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1273,20 +1273,20 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="M12" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P12" t="n">
         <v>117</v>
@@ -1297,7 +1297,11 @@
       <c r="R12" t="n">
         <v>11</v>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - o</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1322,10 +1326,10 @@
         <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>0.397</v>
+        <v>0.392</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1344,14 +1348,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -1423,10 +1427,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="M14" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
@@ -1498,7 +1502,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M15" t="n">
         <v>32.5</v>
@@ -1573,10 +1577,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M16" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -1694,13 +1698,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.753</v>
+        <v>0.757</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1719,11 +1723,11 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>W 7</t>
+          <t>W 8</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1914,10 +1918,10 @@
         <v>45</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>0.616</v>
+        <v>0.608</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1936,14 +1940,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="M21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="N21" t="n">
         <v>3</v>
@@ -1955,7 +1959,7 @@
         <v>114</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
         <v>5</v>
@@ -2014,7 +2018,7 @@
         <v>13.5</v>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="N22" t="n">
         <v>2</v>
@@ -2053,17 +2057,17 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23" t="n">
         <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>0.548</v>
+        <v>0.554</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25-21</t>
+          <t>26-21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2078,26 +2082,26 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="M23" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P23" t="n">
         <v>111</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
         <v>7</v>
@@ -2319,11 +2323,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2340,33 +2344,33 @@
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>16-30</t>
+          <t>19-29</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="M27" t="n">
         <v>31</v>
@@ -2394,11 +2398,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2412,39 +2416,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
-        <v>0.329</v>
+        <v>0.333</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>19-29</t>
+          <t>16-30</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>33.5</v>
       </c>
       <c r="M28" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -2519,7 +2523,7 @@
         <v>34</v>
       </c>
       <c r="M29" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
@@ -2565,14 +2569,14 @@
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G30" t="n">
-        <v>0.284</v>
+        <v>0.28</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11-34</t>
+          <t>11-35</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2582,25 +2586,25 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M30" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P30" t="n">
         <v>125</v>
@@ -2640,10 +2644,10 @@
         <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G31" t="n">
-        <v>0.257</v>
+        <v>0.253</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2657,19 +2661,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="M31" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2852,7 +2856,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2923,7 +2927,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>1.5</v>
@@ -2994,7 +2998,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M4" t="n">
         <v>8</v>
@@ -3036,17 +3040,17 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.548</v>
+        <v>0.554</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>23-23</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3056,19 +3060,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L5" t="n">
         <v>13</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -3077,7 +3081,7 @@
         <v>116</v>
       </c>
       <c r="P5" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -3136,7 +3140,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
         <v>32.5</v>
@@ -3182,13 +3186,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0.726</v>
+        <v>0.73</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3207,7 +3211,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -3223,7 +3227,7 @@
         <v>118</v>
       </c>
       <c r="P7" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q7" t="n">
         <v>8</v>
@@ -3286,10 +3290,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -3331,10 +3335,10 @@
         <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>0.403</v>
+        <v>0.397</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3353,20 +3357,20 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="M9" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P9" t="n">
         <v>117</v>
@@ -3377,7 +3381,11 @@
       <c r="R9" t="n">
         <v>11</v>
       </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - o</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3402,10 +3410,10 @@
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>0.397</v>
+        <v>0.392</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3424,14 +3432,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -3503,10 +3511,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -3698,10 +3706,10 @@
         <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" t="n">
-        <v>0.616</v>
+        <v>0.608</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3720,14 +3728,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="M14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
@@ -3739,7 +3747,7 @@
         <v>114</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
         <v>5</v>
@@ -3840,14 +3848,14 @@
         <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>0.284</v>
+        <v>0.28</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-34</t>
+          <t>11-35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3857,25 +3865,25 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M16" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P16" t="n">
         <v>125</v>
@@ -3983,17 +3991,17 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F18" t="n">
         <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>0.548</v>
+        <v>0.554</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>25-21</t>
+          <t>26-21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4008,26 +4016,26 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="M18" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P18" t="n">
         <v>111</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>7</v>
@@ -4199,10 +4207,10 @@
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>0.257</v>
+        <v>0.253</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4216,19 +4224,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4271,13 +4279,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F22" t="n">
         <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0.554</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -4296,7 +4304,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -4324,11 +4332,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4352,29 +4360,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -4383,10 +4391,10 @@
         <v>116</v>
       </c>
       <c r="P23" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>8</v>
@@ -4395,11 +4403,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4416,19 +4424,19 @@
         <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>0.534</v>
+        <v>0.527</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>23-21</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4438,26 +4446,26 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M24" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P24" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
         <v>9</v>
@@ -4466,11 +4474,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4494,17 +4502,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-21</t>
+          <t>23-23</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -4513,22 +4521,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P25" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>
@@ -4584,10 +4592,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="M26" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -4630,13 +4638,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F27" t="n">
         <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>0.753</v>
+        <v>0.757</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -4655,11 +4663,11 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>W 7</t>
+          <t>W 8</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4737,7 +4745,7 @@
         <v>13.5</v>
       </c>
       <c r="M28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
@@ -4758,11 +4766,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4779,33 +4787,33 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G29" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16-30</t>
+          <t>19-29</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="M29" t="n">
         <v>31</v>
@@ -4833,11 +4841,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4851,39 +4859,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G30" t="n">
-        <v>0.329</v>
+        <v>0.333</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19-29</t>
+          <t>16-30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>33.5</v>
       </c>
       <c r="M30" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -4958,7 +4966,7 @@
         <v>34</v>
       </c>
       <c r="M31" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -1088,11 +1088,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23-21</t>
+          <t>23-23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1144,13 +1144,13 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P10" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
         <v>9</v>
@@ -1159,11 +1159,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1180,48 +1180,48 @@
         <v>39</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>0.527</v>
+        <v>0.52</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>23-23</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P11" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
@@ -1251,10 +1251,10 @@
         <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>0.397</v>
+        <v>0.392</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1273,14 +1273,14 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1548,17 +1548,17 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" t="n">
         <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>0.216</v>
+        <v>0.227</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12-33</t>
+          <t>13-33</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1568,19 +1568,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="M16" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -1592,7 +1592,7 @@
         <v>121</v>
       </c>
       <c r="Q16" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R16" t="n">
         <v>15</v>
@@ -2128,13 +2128,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
         <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.514</v>
+        <v>0.52</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2153,14 +2153,14 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -3335,10 +3335,10 @@
         <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>0.397</v>
+        <v>0.392</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3357,14 +3357,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -3482,17 +3482,17 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
         <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>0.216</v>
+        <v>0.227</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12-33</t>
+          <t>13-33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3502,19 +3502,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="M11" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -3526,7 +3526,7 @@
         <v>121</v>
       </c>
       <c r="Q11" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R11" t="n">
         <v>15</v>
@@ -4062,13 +4062,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F19" t="n">
         <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>0.514</v>
+        <v>0.52</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -4087,14 +4087,14 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -4403,11 +4403,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4431,17 +4431,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23-21</t>
+          <t>23-23</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4459,13 +4459,13 @@
         <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P24" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
         <v>9</v>
@@ -4474,11 +4474,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4495,48 +4495,48 @@
         <v>39</v>
       </c>
       <c r="F25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>0.527</v>
+        <v>0.52</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-23</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="M25" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P25" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>0.671</v>
+        <v>0.676</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30-14</t>
+          <t>31-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -658,7 +658,11 @@
       <c r="R3" t="n">
         <v>2</v>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -683,10 +687,10 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.649</v>
+        <v>0.64</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -705,14 +709,14 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -724,7 +728,7 @@
         <v>111</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
         <v>3</v>
@@ -822,17 +826,17 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>29-16</t>
+          <t>30-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -842,16 +846,16 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
         <v>8</v>
@@ -996,7 +1000,7 @@
         <v>13</v>
       </c>
       <c r="M8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
@@ -1038,14 +1042,14 @@
         <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>0.534</v>
+        <v>0.527</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>24-24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1055,31 +1059,31 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P9" t="n">
         <v>115</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>8</v>
@@ -1088,11 +1092,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1109,48 +1113,48 @@
         <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.527</v>
+        <v>0.52</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23-23</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P10" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>9</v>
@@ -1159,11 +1163,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1187,17 +1191,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>23-24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1215,13 +1219,13 @@
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P11" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
@@ -1380,11 +1384,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1394,26 +1398,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>0.233</v>
+        <v>0.24</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11-34</t>
+          <t>12-32</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>3-12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1423,26 +1427,26 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>36.5</v>
       </c>
       <c r="M14" t="n">
-        <v>24</v>
+        <v>32.5</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="P14" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="R14" t="n">
         <v>13</v>
@@ -1455,11 +1459,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1469,7 +1473,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1483,41 +1487,41 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12-32</t>
+          <t>11-34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>2-12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L 10</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>32.5</v>
+        <v>24.5</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P15" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="Q15" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="R15" t="n">
         <v>14</v>
@@ -1623,13 +1627,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.784</v>
+        <v>0.787</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1648,7 +1652,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1727,7 +1731,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1802,7 +1806,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1844,17 +1848,17 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20" t="n">
         <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>0.627</v>
+        <v>0.632</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29-16</t>
+          <t>30-16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1869,7 +1873,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>W 6</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1888,7 +1892,7 @@
         <v>117</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
         <v>4</v>
@@ -1944,10 +1948,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="N21" t="n">
         <v>3</v>
@@ -1986,22 +1990,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
         <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24-22</t>
+          <t>25-22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2011,14 +2015,14 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L22" t="n">
         <v>13.5</v>
       </c>
       <c r="M22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="N22" t="n">
         <v>2</v>
@@ -2086,7 +2090,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="M23" t="n">
         <v>7</v>
@@ -2157,7 +2161,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M24" t="n">
         <v>9.5</v>
@@ -2199,13 +2203,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F25" t="n">
         <v>38</v>
       </c>
       <c r="G25" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2219,12 +2223,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -2240,7 +2244,7 @@
         <v>115</v>
       </c>
       <c r="P25" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q25" t="n">
         <v>-1</v>
@@ -2273,14 +2277,14 @@
         <v>36</v>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G26" t="n">
-        <v>0.486</v>
+        <v>0.48</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>23-23</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2295,14 +2299,14 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
@@ -2370,7 +2374,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="M27" t="n">
         <v>31</v>
@@ -2419,36 +2423,36 @@
         <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G28" t="n">
-        <v>0.333</v>
+        <v>0.329</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16-30</t>
+          <t>16-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="M28" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -2457,7 +2461,7 @@
         <v>115</v>
       </c>
       <c r="P28" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q28" t="n">
         <v>-4</v>
@@ -2520,7 +2524,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="M29" t="n">
         <v>32</v>
@@ -2595,10 +2599,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M30" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
@@ -2644,10 +2648,10 @@
         <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G31" t="n">
-        <v>0.253</v>
+        <v>0.25</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2661,19 +2665,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="M31" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2827,17 +2831,17 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.671</v>
+        <v>0.676</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30-14</t>
+          <t>31-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2852,11 +2856,11 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2876,7 +2880,11 @@
       <c r="R2" t="n">
         <v>2</v>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2901,10 +2909,10 @@
         <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.649</v>
+        <v>0.64</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2923,14 +2931,14 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -2942,7 +2950,7 @@
         <v>111</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
         <v>3</v>
@@ -2969,17 +2977,17 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>29-16</t>
+          <t>30-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2989,16 +2997,16 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
         <v>8</v>
@@ -3072,7 +3080,7 @@
         <v>13</v>
       </c>
       <c r="M5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -3111,13 +3119,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
         <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3131,16 +3139,16 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L 10</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>36.5</v>
       </c>
       <c r="M6" t="n">
         <v>32.5</v>
@@ -3152,13 +3160,13 @@
         <v>106</v>
       </c>
       <c r="P6" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q6" t="n">
         <v>-9</v>
       </c>
       <c r="R6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -3557,13 +3565,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.784</v>
+        <v>0.787</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3582,7 +3590,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -3632,17 +3640,17 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.627</v>
+        <v>0.632</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>29-16</t>
+          <t>30-16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3657,7 +3665,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>W 6</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -3676,7 +3684,7 @@
         <v>117</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
         <v>4</v>
@@ -3732,10 +3740,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
@@ -3774,13 +3782,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" t="n">
         <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3794,12 +3802,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -3815,7 +3823,7 @@
         <v>115</v>
       </c>
       <c r="P15" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q15" t="n">
         <v>-1</v>
@@ -3874,10 +3882,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M16" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -3949,7 +3957,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -4020,7 +4028,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="M18" t="n">
         <v>7</v>
@@ -4091,7 +4099,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="M19" t="n">
         <v>9.5</v>
@@ -4136,14 +4144,14 @@
         <v>36</v>
       </c>
       <c r="F20" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>0.486</v>
+        <v>0.48</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>23-23</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4158,14 +4166,14 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="N20" t="n">
         <v>4</v>
@@ -4207,10 +4215,10 @@
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>0.253</v>
+        <v>0.25</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4224,19 +4232,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="M21" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4353,14 +4361,14 @@
         <v>39</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.534</v>
+        <v>0.527</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>24-24</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -4370,31 +4378,31 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P23" t="n">
         <v>115</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>8</v>
@@ -4403,11 +4411,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4424,48 +4432,48 @@
         <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.527</v>
+        <v>0.52</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23-23</t>
+          <t>23-22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="M24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P24" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
         <v>9</v>
@@ -4474,11 +4482,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4502,17 +4510,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>23-24</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -4530,13 +4538,13 @@
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P25" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>
@@ -4566,10 +4574,10 @@
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G26" t="n">
-        <v>0.233</v>
+        <v>0.23</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4588,14 +4596,14 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M26" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -4610,7 +4618,7 @@
         <v>-11</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -4667,7 +4675,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4713,22 +4721,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F28" t="n">
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>24-22</t>
+          <t>25-22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4738,14 +4746,14 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>13.5</v>
       </c>
       <c r="M28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
@@ -4813,7 +4821,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="M29" t="n">
         <v>31</v>
@@ -4862,36 +4870,36 @@
         <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G30" t="n">
-        <v>0.333</v>
+        <v>0.329</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>16-30</t>
+          <t>16-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="M30" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -4900,7 +4908,7 @@
         <v>115</v>
       </c>
       <c r="P30" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" t="n">
         <v>-4</v>
@@ -4963,7 +4971,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="M31" t="n">
         <v>32</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -534,17 +534,17 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.73</v>
+        <v>0.724</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>34-12</t>
+          <t>35-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -575,7 +575,7 @@
         <v>118</v>
       </c>
       <c r="P2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q2" t="n">
         <v>8</v>
@@ -585,7 +585,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - x</t>
+          <t xml:space="preserve"> - c</t>
         </is>
       </c>
     </row>
@@ -612,14 +612,14 @@
         <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.676</v>
+        <v>0.667</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31-14</t>
+          <t>31-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -687,10 +687,10 @@
         <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.64</v>
+        <v>0.632</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -709,11 +709,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
         <v>2.5</v>
@@ -733,7 +733,11 @@
       <c r="R4" t="n">
         <v>3</v>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -755,13 +759,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.622</v>
+        <v>0.627</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -780,14 +784,14 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M5" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
@@ -808,11 +812,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -822,31 +826,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30-16</t>
+          <t>24-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -858,16 +862,16 @@
         <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="P6" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="Q6" t="n">
         <v>2</v>
@@ -879,11 +883,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -893,7 +897,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -907,38 +911,38 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>30-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L7" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P7" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
@@ -971,14 +975,14 @@
         <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>0.554</v>
+        <v>0.547</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>24-24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -988,16 +992,16 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M8" t="n">
         <v>9</v>
@@ -1009,7 +1013,7 @@
         <v>116</v>
       </c>
       <c r="P8" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1039,13 +1043,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
         <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>0.527</v>
+        <v>0.533</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1064,11 +1068,11 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="M9" t="n">
         <v>2.5</v>
@@ -1110,17 +1114,17 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.52</v>
+        <v>0.526</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>24-22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1135,11 +1139,11 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
         <v>3</v>
@@ -1181,17 +1185,17 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
         <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>0.52</v>
+        <v>0.526</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>23-24</t>
+          <t>24-24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1206,11 +1210,11 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
@@ -1222,10 +1226,10 @@
         <v>116</v>
       </c>
       <c r="P11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
@@ -1252,13 +1256,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
         <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>0.392</v>
+        <v>0.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1272,25 +1276,25 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="M12" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P12" t="n">
         <v>117</v>
@@ -1330,10 +1334,10 @@
         <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>0.392</v>
+        <v>0.387</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1347,19 +1351,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="M13" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -1405,14 +1409,14 @@
         <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" t="n">
-        <v>0.24</v>
+        <v>0.237</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12-32</t>
+          <t>12-33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1427,11 +1431,11 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M14" t="n">
         <v>32.5</v>
@@ -1480,10 +1484,10 @@
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0.23</v>
+        <v>0.227</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1502,20 +1506,20 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M15" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P15" t="n">
         <v>124</v>
@@ -1627,13 +1631,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.787</v>
+        <v>0.789</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1652,7 +1656,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1702,13 +1706,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F18" t="n">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.757</v>
+        <v>0.76</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1727,7 +1731,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>W 8</t>
+          <t>W 9</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1740,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P18" t="n">
         <v>111</v>
@@ -1777,13 +1781,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.649</v>
+        <v>0.653</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1802,7 +1806,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1826,7 +1830,11 @@
       <c r="R19" t="n">
         <v>3</v>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - p</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1877,10 +1885,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N20" t="n">
         <v>2</v>
@@ -1897,7 +1905,11 @@
       <c r="R20" t="n">
         <v>4</v>
       </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1919,17 +1931,17 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F21" t="n">
         <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>0.608</v>
+        <v>0.613</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>28-21</t>
+          <t>29-21</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1939,12 +1951,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1963,7 +1975,7 @@
         <v>114</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
         <v>5</v>
@@ -1990,13 +2002,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
         <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.608</v>
+        <v>0.613</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2010,12 +2022,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -2061,17 +2073,17 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>0.554</v>
+        <v>0.553</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>26-21</t>
+          <t>27-21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2081,19 +2093,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -2161,10 +2173,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="M24" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -2232,10 +2244,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="M25" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
@@ -2303,10 +2315,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="M26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
@@ -2348,14 +2360,14 @@
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>19-29</t>
+          <t>19-30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2370,14 +2382,14 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="M27" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
@@ -2449,10 +2461,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="M28" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -2498,14 +2510,14 @@
         <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G29" t="n">
-        <v>0.324</v>
+        <v>0.316</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>13-33</t>
+          <t>13-34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2515,31 +2527,31 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>34.5</v>
+        <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>32</v>
+        <v>33.5</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P29" t="n">
         <v>119</v>
       </c>
       <c r="Q29" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R29" t="n">
         <v>13</v>
@@ -2573,10 +2585,10 @@
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G30" t="n">
-        <v>0.28</v>
+        <v>0.276</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2595,14 +2607,14 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M30" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
@@ -2674,10 +2686,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>40.5</v>
+        <v>41</v>
       </c>
       <c r="M31" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2834,14 +2846,14 @@
         <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.676</v>
+        <v>0.667</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31-14</t>
+          <t>31-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2856,11 +2868,11 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2909,10 +2921,10 @@
         <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.64</v>
+        <v>0.632</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2931,11 +2943,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>2.5</v>
@@ -2955,7 +2967,11 @@
       <c r="R3" t="n">
         <v>3</v>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2980,14 +2996,14 @@
         <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>30-16</t>
+          <t>30-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3002,11 +3018,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M4" t="n">
         <v>8</v>
@@ -3024,7 +3040,7 @@
         <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S4" t="inlineStr"/>
     </row>
@@ -3051,14 +3067,14 @@
         <v>41</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.554</v>
+        <v>0.547</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>24-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3068,16 +3084,16 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M5" t="n">
         <v>9</v>
@@ -3089,7 +3105,7 @@
         <v>116</v>
       </c>
       <c r="P5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -3122,14 +3138,14 @@
         <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>0.24</v>
+        <v>0.237</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12-32</t>
+          <t>12-33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3144,11 +3160,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
         <v>32.5</v>
@@ -3194,17 +3210,17 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.73</v>
+        <v>0.724</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>34-12</t>
+          <t>35-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3214,12 +3230,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -3235,7 +3251,7 @@
         <v>118</v>
       </c>
       <c r="P7" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q7" t="n">
         <v>8</v>
@@ -3245,7 +3261,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - x</t>
+          <t xml:space="preserve"> - c</t>
         </is>
       </c>
     </row>
@@ -3269,13 +3285,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
         <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.622</v>
+        <v>0.627</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3294,14 +3310,14 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -3340,13 +3356,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
         <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>0.392</v>
+        <v>0.4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3360,25 +3376,25 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P9" t="n">
         <v>117</v>
@@ -3418,10 +3434,10 @@
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>0.392</v>
+        <v>0.387</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3435,19 +3451,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="M10" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -3565,13 +3581,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.787</v>
+        <v>0.789</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3590,7 +3606,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -3669,10 +3685,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -3689,7 +3705,11 @@
       <c r="R13" t="n">
         <v>4</v>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3711,17 +3731,17 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" t="n">
         <v>29</v>
       </c>
       <c r="G14" t="n">
-        <v>0.608</v>
+        <v>0.613</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28-21</t>
+          <t>29-21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3731,12 +3751,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -3755,7 +3775,7 @@
         <v>114</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
         <v>5</v>
@@ -3811,10 +3831,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="M15" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
@@ -3856,10 +3876,10 @@
         <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>0.28</v>
+        <v>0.276</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -3878,14 +3898,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -3928,13 +3948,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
         <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>0.649</v>
+        <v>0.653</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3953,7 +3973,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -3977,7 +3997,11 @@
       <c r="R17" t="n">
         <v>3</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - p</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3999,17 +4023,17 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>0.554</v>
+        <v>0.553</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>26-21</t>
+          <t>27-21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4019,19 +4043,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -4099,10 +4123,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="M19" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -4170,10 +4194,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="M20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="N20" t="n">
         <v>4</v>
@@ -4241,10 +4265,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>40.5</v>
+        <v>41</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4287,17 +4311,17 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" t="n">
         <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>24-22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4312,11 +4336,11 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4334,7 +4358,7 @@
         <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S22" t="inlineStr"/>
     </row>
@@ -4358,13 +4382,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F23" t="n">
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.527</v>
+        <v>0.533</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -4383,11 +4407,11 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="M23" t="n">
         <v>2.5</v>
@@ -4429,17 +4453,17 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F24" t="n">
         <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.52</v>
+        <v>0.526</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23-22</t>
+          <t>24-22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -4454,11 +4478,11 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
@@ -4500,17 +4524,17 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F25" t="n">
         <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>0.52</v>
+        <v>0.526</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23-24</t>
+          <t>24-24</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4525,11 +4549,11 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
         <v>3</v>
@@ -4541,10 +4565,10 @@
         <v>116</v>
       </c>
       <c r="P25" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>
@@ -4574,10 +4598,10 @@
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G26" t="n">
-        <v>0.23</v>
+        <v>0.227</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -4596,20 +4620,20 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M26" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P26" t="n">
         <v>124</v>
@@ -4646,13 +4670,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F27" t="n">
         <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>0.757</v>
+        <v>0.76</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -4671,7 +4695,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>W 8</t>
+          <t>W 9</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -4684,7 +4708,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P27" t="n">
         <v>111</v>
@@ -4721,13 +4745,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F28" t="n">
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.608</v>
+        <v>0.613</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -4741,12 +4765,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -4795,14 +4819,14 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G29" t="n">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19-29</t>
+          <t>19-30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4817,14 +4841,14 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="M29" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
@@ -4896,10 +4920,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="M30" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -4945,14 +4969,14 @@
         <v>24</v>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G31" t="n">
-        <v>0.324</v>
+        <v>0.316</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13-33</t>
+          <t>13-34</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4962,31 +4986,31 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>34.5</v>
+        <v>36</v>
       </c>
       <c r="M31" t="n">
-        <v>32</v>
+        <v>33.5</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P31" t="n">
         <v>119</v>
       </c>
       <c r="Q31" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R31" t="n">
         <v>13</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -762,10 +762,10 @@
         <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>0.627</v>
+        <v>0.618</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -784,14 +784,14 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
@@ -1781,13 +1781,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.653</v>
+        <v>0.658</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1806,11 +1806,11 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>18</v>
       </c>
       <c r="M23" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -2147,14 +2147,14 @@
         <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.52</v>
+        <v>0.513</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>22-23</t>
+          <t>22-24</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2164,19 +2164,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -2215,17 +2215,17 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F25" t="n">
         <v>38</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25-21</t>
+          <t>26-21</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2240,14 +2240,14 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="M25" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
@@ -2318,7 +2318,7 @@
         <v>23.5</v>
       </c>
       <c r="M26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
@@ -2689,7 +2689,7 @@
         <v>41</v>
       </c>
       <c r="M31" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -3288,10 +3288,10 @@
         <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.627</v>
+        <v>0.618</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3310,14 +3310,14 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -3802,17 +3802,17 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
         <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>25-21</t>
+          <t>26-21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3827,14 +3827,14 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="M15" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
@@ -3948,13 +3948,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
         <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>0.653</v>
+        <v>0.658</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3973,11 +3973,11 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         <v>18</v>
       </c>
       <c r="M18" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -4097,14 +4097,14 @@
         <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.52</v>
+        <v>0.513</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-23</t>
+          <t>22-24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4114,19 +4114,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -4197,7 +4197,7 @@
         <v>23.5</v>
       </c>
       <c r="M20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="N20" t="n">
         <v>4</v>
@@ -4268,7 +4268,7 @@
         <v>41</v>
       </c>
       <c r="M21" t="n">
-        <v>30.5</v>
+        <v>31</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.667</v>
+        <v>0.671</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31-15</t>
+          <t>32-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -629,16 +629,16 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -684,13 +684,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.632</v>
+        <v>0.636</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -709,11 +709,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
         <v>2.5</v>
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>24-22</t>
+          <t>25-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -855,11 +855,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -883,11 +883,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -904,48 +904,48 @@
         <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.553</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30-17</t>
+          <t>25-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="M7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P7" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>6</v>
@@ -954,11 +954,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -972,36 +972,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
         <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>0.547</v>
+        <v>0.553</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>24-24</t>
+          <t>30-17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M8" t="n">
         <v>9</v>
@@ -1010,13 +1010,13 @@
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="P8" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>7</v>
@@ -1025,11 +1025,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1046,10 +1046,10 @@
         <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>0.533</v>
+        <v>0.526</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1072,22 +1072,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P9" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
         <v>8</v>
@@ -1096,11 +1096,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1124,41 +1124,41 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>24-22</t>
+          <t>24-25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L10" t="n">
         <v>15</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="P10" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>9</v>
@@ -1167,11 +1167,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1188,48 +1188,48 @@
         <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>0.526</v>
+        <v>0.519</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>24-24</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P11" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
@@ -1259,10 +1259,10 @@
         <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1281,14 +1281,14 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="M12" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1334,19 +1334,19 @@
         <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>0.387</v>
+        <v>0.382</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-29</t>
+          <t>17-30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>4-12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="M13" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -1388,11 +1388,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1416,41 +1416,41 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12-33</t>
+          <t>14-33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>37</v>
       </c>
       <c r="M14" t="n">
-        <v>32.5</v>
+        <v>37</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P14" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R14" t="n">
         <v>13</v>
@@ -1463,11 +1463,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1477,26 +1477,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
         <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0.227</v>
+        <v>0.237</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11-34</t>
+          <t>12-33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>3-12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1506,26 +1506,26 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>25.5</v>
+        <v>33</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="P15" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="Q15" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="R15" t="n">
         <v>14</v>
@@ -1538,11 +1538,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1610612754</v>
+        <v>1610612764</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1552,55 +1552,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>17</v>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G16" t="n">
-        <v>0.227</v>
+        <v>0.224</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13-33</t>
+          <t>11-35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3-10</t>
+          <t>2-12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M16" t="n">
-        <v>37.5</v>
+        <v>26.5</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P16" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="R16" t="n">
         <v>15</v>
@@ -1706,17 +1706,17 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" t="n">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.76</v>
+        <v>0.763</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>32-14</t>
+          <t>33-14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1726,16 +1726,16 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>10-0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>W 9</t>
+          <t>W 10</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F20" t="n">
         <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>0.632</v>
+        <v>0.636</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30-16</t>
+          <t>31-16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8-5</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1881,14 +1881,14 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>W 6</t>
+          <t>W 7</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N20" t="n">
         <v>2</v>
@@ -1913,11 +1913,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Rockets</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1927,26 +1927,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Northwest</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F21" t="n">
         <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>0.613</v>
+        <v>0.618</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>29-21</t>
+          <t>25-22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,23 +1956,23 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M21" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P21" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
@@ -1984,11 +1984,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Timberwolves</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Northwest</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>25-22</t>
+          <t>29-21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,23 +2027,23 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L22" t="n">
         <v>13.5</v>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
+        <v>118</v>
+      </c>
+      <c r="P22" t="n">
         <v>114</v>
-      </c>
-      <c r="P22" t="n">
-        <v>110</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
@@ -2289,14 +2289,14 @@
         <v>36</v>
       </c>
       <c r="F26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>0.48</v>
+        <v>0.474</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23-23</t>
+          <t>23-24</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2311,14 +2311,14 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="M26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
@@ -2339,11 +2339,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2360,36 +2360,36 @@
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G27" t="n">
-        <v>0.333</v>
+        <v>0.329</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>19-30</t>
+          <t>16-31</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="M27" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
@@ -2398,7 +2398,7 @@
         <v>115</v>
       </c>
       <c r="P27" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q27" t="n">
         <v>-4</v>
@@ -2414,11 +2414,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2442,29 +2442,29 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16-31</t>
+          <t>19-30</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>35</v>
       </c>
       <c r="M28" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -2473,7 +2473,7 @@
         <v>115</v>
       </c>
       <c r="P28" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q28" t="n">
         <v>-4</v>
@@ -2539,7 +2539,7 @@
         <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
@@ -2585,19 +2585,19 @@
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G30" t="n">
-        <v>0.276</v>
+        <v>0.273</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11-35</t>
+          <t>11-36</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1-13</t>
+          <t>1-14</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2607,14 +2607,14 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>L 7</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="M30" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F31" t="n">
         <v>57</v>
       </c>
       <c r="G31" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2677,19 +2677,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="M31" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2843,17 +2843,17 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
         <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.667</v>
+        <v>0.671</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31-15</t>
+          <t>32-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2863,16 +2863,16 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
         <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.632</v>
+        <v>0.636</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2943,11 +2943,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>2.5</v>
@@ -2975,11 +2975,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2996,48 +2996,48 @@
         <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.553</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>30-17</t>
+          <t>25-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P4" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>6</v>
@@ -3046,11 +3046,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3064,36 +3064,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
         <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.547</v>
+        <v>0.553</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>24-24</t>
+          <t>30-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M5" t="n">
         <v>9</v>
@@ -3102,13 +3102,13 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="P5" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
@@ -3167,7 +3167,7 @@
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -3182,7 +3182,7 @@
         <v>-9</v>
       </c>
       <c r="R6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3381,14 +3381,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -3434,19 +3434,19 @@
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>0.387</v>
+        <v>0.382</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-29</t>
+          <t>17-30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>4-12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3456,14 +3456,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="M10" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -3506,45 +3506,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
         <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>0.227</v>
+        <v>0.237</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13-33</t>
+          <t>14-33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3-10</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P11" t="n">
         <v>121</v>
@@ -3553,7 +3553,7 @@
         <v>-8</v>
       </c>
       <c r="R11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -3656,22 +3656,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.632</v>
+        <v>0.636</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30-16</t>
+          <t>31-16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8-5</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>W 6</t>
+          <t>W 7</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -3778,7 +3778,7 @@
         <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S14" t="inlineStr"/>
     </row>
@@ -3876,19 +3876,19 @@
         <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>0.276</v>
+        <v>0.273</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-35</t>
+          <t>11-36</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1-13</t>
+          <t>1-14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3898,14 +3898,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>L 7</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="M16" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -4168,14 +4168,14 @@
         <v>36</v>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.48</v>
+        <v>0.474</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23-23</t>
+          <t>23-24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4190,14 +4190,14 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="M20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="N20" t="n">
         <v>4</v>
@@ -4236,13 +4236,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
         <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4256,19 +4256,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="M21" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4311,22 +4311,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
         <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24-22</t>
+          <t>25-22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4336,11 +4336,11 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4364,11 +4364,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4385,10 +4385,10 @@
         <v>40</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>0.533</v>
+        <v>0.526</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4411,22 +4411,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="M23" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P23" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
         <v>8</v>
@@ -4435,11 +4435,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4463,41 +4463,41 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24-22</t>
+          <t>24-25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>15</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="P24" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>9</v>
@@ -4506,11 +4506,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4527,48 +4527,48 @@
         <v>40</v>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>0.526</v>
+        <v>0.519</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24-24</t>
+          <t>24-23</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P25" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>
@@ -4598,14 +4598,14 @@
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G26" t="n">
-        <v>0.227</v>
+        <v>0.224</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-34</t>
+          <t>11-35</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4620,29 +4620,29 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M26" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P26" t="n">
         <v>124</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -4670,17 +4670,17 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F27" t="n">
         <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>0.76</v>
+        <v>0.763</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>32-14</t>
+          <t>33-14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4690,16 +4690,16 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>10-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>W 9</t>
+          <t>W 10</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F28" t="n">
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.613</v>
+        <v>0.618</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -4770,11 +4770,11 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M28" t="n">
         <v>11</v>
@@ -4792,17 +4792,17 @@
         <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4819,36 +4819,36 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G29" t="n">
-        <v>0.333</v>
+        <v>0.329</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19-30</t>
+          <t>16-31</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="M29" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
@@ -4857,7 +4857,7 @@
         <v>115</v>
       </c>
       <c r="P29" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q29" t="n">
         <v>-4</v>
@@ -4873,11 +4873,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4901,29 +4901,29 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>16-31</t>
+          <t>19-30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>35</v>
       </c>
       <c r="M30" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -4932,7 +4932,7 @@
         <v>115</v>
       </c>
       <c r="P30" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q30" t="n">
         <v>-4</v>
@@ -4998,7 +4998,7 @@
         <v>36</v>
       </c>
       <c r="M31" t="n">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.724</v>
+        <v>0.727</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,12 +554,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P2" t="n">
         <v>110</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
         <v>2.5</v>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>0.618</v>
+        <v>0.623</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -808,7 +808,11 @@
       <c r="R5" t="n">
         <v>4</v>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -859,7 +863,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -930,7 +934,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M7" t="n">
         <v>9</v>
@@ -1001,7 +1005,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M8" t="n">
         <v>9</v>
@@ -1043,13 +1047,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>0.526</v>
+        <v>0.532</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1068,14 +1072,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L9" t="n">
         <v>15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1143,7 +1147,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="M10" t="n">
         <v>3.5</v>
@@ -1214,7 +1218,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="M11" t="n">
         <v>4</v>
@@ -1285,10 +1289,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="M12" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1360,10 +1364,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -1435,10 +1439,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M14" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
@@ -1510,7 +1514,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M15" t="n">
         <v>33</v>
@@ -1585,7 +1589,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="M16" t="n">
         <v>26.5</v>
@@ -1631,17 +1635,17 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.789</v>
+        <v>0.792</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>37-9</t>
+          <t>38-9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1672,7 +1676,7 @@
         <v>119</v>
       </c>
       <c r="P17" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q17" t="n">
         <v>11</v>
@@ -1706,17 +1710,17 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.763</v>
+        <v>0.766</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>33-14</t>
+          <t>34-14</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1731,7 +1735,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>W 10</t>
+          <t>W 11</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1784,14 +1788,14 @@
         <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>0.658</v>
+        <v>0.649</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>30-16</t>
+          <t>30-17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1801,16 +1805,16 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1885,10 +1889,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N20" t="n">
         <v>2</v>
@@ -1960,10 +1964,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="N21" t="n">
         <v>2</v>
@@ -1980,7 +1984,11 @@
       <c r="R21" t="n">
         <v>5</v>
       </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2005,10 +2013,10 @@
         <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>0.613</v>
+        <v>0.605</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2027,14 +2035,14 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="M22" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
@@ -2076,10 +2084,10 @@
         <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.553</v>
+        <v>0.545</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2098,11 +2106,11 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M23" t="n">
         <v>8</v>
@@ -2117,7 +2125,7 @@
         <v>111</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>7</v>
@@ -2126,11 +2134,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2140,55 +2148,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Northwest</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G24" t="n">
         <v>0.513</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>22-24</t>
+          <t>27-21</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="M24" t="n">
-        <v>11</v>
+        <v>21.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P24" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R24" t="n">
         <v>8</v>
@@ -2197,11 +2205,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2211,7 +2219,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Northwest</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2225,41 +2233,41 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>26-21</t>
+          <t>22-25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="M25" t="n">
-        <v>21.5</v>
+        <v>11</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P25" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>9</v>
@@ -2289,10 +2297,10 @@
         <v>36</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G26" t="n">
-        <v>0.474</v>
+        <v>0.468</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2311,11 +2319,11 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M26" t="n">
         <v>14</v>
@@ -2339,11 +2347,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2367,29 +2375,29 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>16-31</t>
+          <t>19-30</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="M27" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
@@ -2398,7 +2406,7 @@
         <v>115</v>
       </c>
       <c r="P27" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q27" t="n">
         <v>-4</v>
@@ -2414,11 +2422,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2435,36 +2443,36 @@
         <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G28" t="n">
-        <v>0.329</v>
+        <v>0.325</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>19-30</t>
+          <t>16-32</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -2476,7 +2484,7 @@
         <v>119</v>
       </c>
       <c r="Q28" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R28" t="n">
         <v>12</v>
@@ -2536,10 +2544,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="M29" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
@@ -2611,10 +2619,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
@@ -2686,10 +2694,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>40.5</v>
+        <v>41</v>
       </c>
       <c r="M31" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2872,7 +2880,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2947,7 +2955,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>2.5</v>
@@ -3022,7 +3030,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M4" t="n">
         <v>9</v>
@@ -3093,7 +3101,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M5" t="n">
         <v>9</v>
@@ -3164,7 +3172,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M6" t="n">
         <v>33</v>
@@ -3210,13 +3218,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
         <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.724</v>
+        <v>0.727</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3230,12 +3238,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -3248,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P7" t="n">
         <v>110</v>
@@ -3285,13 +3293,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.618</v>
+        <v>0.623</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3310,7 +3318,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -3334,7 +3342,11 @@
       <c r="R8" t="n">
         <v>4</v>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3385,10 +3397,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -3460,10 +3472,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -3535,10 +3547,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M11" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -3581,17 +3593,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F12" t="n">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.789</v>
+        <v>0.792</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>37-9</t>
+          <t>38-9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3606,7 +3618,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -3622,7 +3634,7 @@
         <v>119</v>
       </c>
       <c r="P12" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
@@ -3685,10 +3697,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -3734,10 +3746,10 @@
         <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>0.613</v>
+        <v>0.605</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3756,14 +3768,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="M14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
@@ -3802,17 +3814,17 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" t="n">
         <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>0.506</v>
+        <v>0.513</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>26-21</t>
+          <t>27-21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3822,12 +3834,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -3849,7 +3861,7 @@
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S15" t="inlineStr"/>
     </row>
@@ -3902,10 +3914,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="M16" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -3951,14 +3963,14 @@
         <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>0.658</v>
+        <v>0.649</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30-16</t>
+          <t>30-17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3968,16 +3980,16 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -4026,10 +4038,10 @@
         <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>0.553</v>
+        <v>0.545</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -4048,11 +4060,11 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M18" t="n">
         <v>8</v>
@@ -4067,7 +4079,7 @@
         <v>111</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>7</v>
@@ -4097,14 +4109,14 @@
         <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>0.513</v>
+        <v>0.506</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-24</t>
+          <t>22-25</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4119,11 +4131,11 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M19" t="n">
         <v>11</v>
@@ -4141,7 +4153,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S19" t="inlineStr"/>
     </row>
@@ -4168,10 +4180,10 @@
         <v>36</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>0.474</v>
+        <v>0.468</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -4190,11 +4202,11 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M20" t="n">
         <v>14</v>
@@ -4265,10 +4277,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>40.5</v>
+        <v>41</v>
       </c>
       <c r="M21" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4340,7 +4352,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4382,13 +4394,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23" t="n">
         <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>0.526</v>
+        <v>0.532</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -4407,14 +4419,14 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -4482,7 +4494,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="M24" t="n">
         <v>3.5</v>
@@ -4553,7 +4565,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="M25" t="n">
         <v>4</v>
@@ -4624,7 +4636,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="M26" t="n">
         <v>26.5</v>
@@ -4670,17 +4682,17 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F27" t="n">
         <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>0.763</v>
+        <v>0.766</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>33-14</t>
+          <t>34-14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4695,7 +4707,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>W 10</t>
+          <t>W 11</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -4774,10 +4786,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
@@ -4794,15 +4806,19 @@
       <c r="R28" t="n">
         <v>5</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4826,29 +4842,29 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16-31</t>
+          <t>19-30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="M29" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
@@ -4857,7 +4873,7 @@
         <v>115</v>
       </c>
       <c r="P29" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q29" t="n">
         <v>-4</v>
@@ -4873,11 +4889,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4894,36 +4910,36 @@
         <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G30" t="n">
-        <v>0.329</v>
+        <v>0.325</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19-30</t>
+          <t>16-32</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M30" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -4935,7 +4951,7 @@
         <v>119</v>
       </c>
       <c r="Q30" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R30" t="n">
         <v>12</v>
@@ -4995,10 +5011,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="M31" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" t="n">
         <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>0.553</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -930,14 +930,14 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
@@ -1047,17 +1047,17 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>0.532</v>
+        <v>0.538</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24-24</t>
+          <t>25-24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1392,11 +1392,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1420,41 +1420,41 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14-33</t>
+          <t>12-33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>3-12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>37.5</v>
       </c>
       <c r="M14" t="n">
-        <v>37.5</v>
+        <v>33</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="P14" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R14" t="n">
         <v>13</v>
@@ -1467,11 +1467,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1481,31 +1481,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>0.237</v>
+        <v>0.234</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12-33</t>
+          <t>14-34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1514,22 +1514,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M15" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P15" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="Q15" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R15" t="n">
         <v>14</v>
@@ -2013,10 +2013,10 @@
         <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G22" t="n">
-        <v>0.605</v>
+        <v>0.597</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2030,19 +2030,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="M22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
@@ -3001,13 +3001,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
         <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>0.553</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -3026,14 +3026,14 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -3190,7 +3190,7 @@
         <v>-9</v>
       </c>
       <c r="R6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -3521,14 +3521,14 @@
         <v>18</v>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>0.237</v>
+        <v>0.234</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14-33</t>
+          <t>14-34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3543,14 +3543,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -3565,7 +3565,7 @@
         <v>-8</v>
       </c>
       <c r="R11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
         <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
-        <v>0.605</v>
+        <v>0.597</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3763,19 +3763,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
@@ -4394,17 +4394,17 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
         <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>0.532</v>
+        <v>0.538</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>24-24</t>
+          <t>25-24</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -4414,19 +4414,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -684,17 +684,17 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.636</v>
+        <v>0.641</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>31-16</t>
+          <t>32-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -709,14 +709,14 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -834,17 +834,17 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
         <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>0.571</v>
+        <v>0.577</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25-22</t>
+          <t>26-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -859,11 +859,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>14.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1150,7 +1150,7 @@
         <v>15.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1221,7 +1221,7 @@
         <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
@@ -1338,14 +1338,14 @@
         <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>0.382</v>
+        <v>0.377</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-30</t>
+          <t>17-31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="M13" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -1392,11 +1392,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1406,31 +1406,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" t="n">
-        <v>0.237</v>
+        <v>0.234</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12-33</t>
+          <t>14-34</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M14" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P14" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R14" t="n">
         <v>13</v>
@@ -1467,11 +1467,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1495,41 +1495,41 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14-34</t>
+          <t>12-34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>3-12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L15" t="n">
         <v>38</v>
       </c>
       <c r="M15" t="n">
-        <v>38</v>
+        <v>33.5</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="P15" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="Q15" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R15" t="n">
         <v>14</v>
@@ -1592,7 +1592,7 @@
         <v>38.5</v>
       </c>
       <c r="M16" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -2926,17 +2926,17 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.636</v>
+        <v>0.641</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31-16</t>
+          <t>32-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2951,14 +2951,14 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -3146,14 +3146,14 @@
         <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>0.237</v>
+        <v>0.234</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12-33</t>
+          <t>12-34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3168,14 +3168,14 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -3190,7 +3190,7 @@
         <v>-9</v>
       </c>
       <c r="R6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -3446,14 +3446,14 @@
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>0.382</v>
+        <v>0.377</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-30</t>
+          <t>17-31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -3565,7 +3565,7 @@
         <v>-8</v>
       </c>
       <c r="R11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -4323,17 +4323,17 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
         <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0.571</v>
+        <v>0.577</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>25-22</t>
+          <t>26-22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4348,11 +4348,11 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         <v>14.5</v>
       </c>
       <c r="M23" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -4497,7 +4497,7 @@
         <v>15.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -4568,7 +4568,7 @@
         <v>16</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
@@ -4639,7 +4639,7 @@
         <v>38.5</v>
       </c>
       <c r="M26" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -534,17 +534,17 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.727</v>
+        <v>0.731</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>35-12</t>
+          <t>36-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -575,7 +575,7 @@
         <v>117</v>
       </c>
       <c r="P2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q2" t="n">
         <v>8</v>
@@ -585,7 +585,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - c</t>
+          <t xml:space="preserve"> - e</t>
         </is>
       </c>
     </row>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.671</v>
+        <v>0.675</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>32-15</t>
+          <t>33-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -647,13 +647,13 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P3" t="n">
         <v>107</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
         <v>2</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -725,10 +725,10 @@
         <v>117</v>
       </c>
       <c r="P4" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
         <v>3</v>
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M5" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -872,13 +872,13 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P6" t="n">
         <v>116</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>5</v>
@@ -887,11 +887,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -915,41 +915,41 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25-24</t>
+          <t>30-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P7" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>6</v>
@@ -958,11 +958,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -976,51 +976,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>0.553</v>
+        <v>0.551</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-17</t>
+          <t>25-25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P8" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>7</v>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="M9" t="n">
         <v>3</v>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" t="n">
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.526</v>
+        <v>0.532</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L10" t="n">
         <v>15.5</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1189,45 +1189,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
         <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>0.519</v>
+        <v>0.526</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>25-23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>8-7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L11" t="n">
         <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P11" t="n">
         <v>118</v>
@@ -1263,14 +1263,14 @@
         <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20-27</t>
+          <t>20-28</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1280,19 +1280,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="M12" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="M13" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -1376,7 +1376,7 @@
         <v>116</v>
       </c>
       <c r="P13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q13" t="n">
         <v>-5</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="M14" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="M15" t="n">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
@@ -1526,10 +1526,10 @@
         <v>106</v>
       </c>
       <c r="P15" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q15" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R15" t="n">
         <v>14</v>
@@ -1563,19 +1563,19 @@
         <v>17</v>
       </c>
       <c r="F16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>0.224</v>
+        <v>0.221</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-35</t>
+          <t>11-36</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>2-13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1585,14 +1585,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="M16" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -1601,7 +1601,7 @@
         <v>113</v>
       </c>
       <c r="P16" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q16" t="n">
         <v>-12</v>
@@ -1713,14 +1713,14 @@
         <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.766</v>
+        <v>0.756</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>34-14</t>
+          <t>34-15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1730,16 +1730,16 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10-0</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>W 11</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1860,17 +1860,17 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
         <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>0.636</v>
+        <v>0.641</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>31-16</t>
+          <t>32-16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1880,25 +1880,25 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>W 7</t>
+          <t>W 8</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N20" t="n">
         <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P20" t="n">
         <v>117</v>
@@ -1935,17 +1935,17 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="n">
         <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>0.618</v>
+        <v>0.623</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>25-22</t>
+          <t>26-22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1955,31 +1955,31 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N21" t="n">
         <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P21" t="n">
         <v>110</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
         <v>5</v>
@@ -2368,10 +2368,10 @@
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G27" t="n">
-        <v>0.329</v>
+        <v>0.325</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2390,11 +2390,11 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="M27" t="n">
         <v>33.5</v>
@@ -2406,10 +2406,10 @@
         <v>115</v>
       </c>
       <c r="P27" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R27" t="n">
         <v>11</v>
@@ -2443,14 +2443,14 @@
         <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G28" t="n">
-        <v>0.325</v>
+        <v>0.321</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16-32</t>
+          <t>16-33</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2465,11 +2465,11 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>L 7</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="M28" t="n">
         <v>34</v>
@@ -2518,10 +2518,10 @@
         <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G29" t="n">
-        <v>0.316</v>
+        <v>0.312</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2540,11 +2540,11 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M29" t="n">
         <v>34.5</v>
@@ -2553,7 +2553,7 @@
         <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P29" t="n">
         <v>119</v>
@@ -2572,11 +2572,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2586,55 +2586,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Northwest</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G30" t="n">
-        <v>0.273</v>
+        <v>0.269</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11-36</t>
+          <t>13-35</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1-14</t>
+          <t>3-10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 7</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="M30" t="n">
-        <v>40</v>
+        <v>29.5</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="P30" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="Q30" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="R30" t="n">
         <v>14</v>
@@ -2647,11 +2647,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2661,55 +2661,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Northwest</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F31" t="n">
         <v>57</v>
       </c>
       <c r="G31" t="n">
-        <v>0.26</v>
+        <v>0.269</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12-35</t>
+          <t>11-37</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3-10</t>
+          <t>1-14</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 8</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="M31" t="n">
-        <v>30</v>
+        <v>40.5</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="P31" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="Q31" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="R31" t="n">
         <v>15</v>
@@ -2851,17 +2851,17 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
         <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.671</v>
+        <v>0.675</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>32-15</t>
+          <t>33-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -2889,13 +2889,13 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P2" t="n">
         <v>107</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -2967,10 +2967,10 @@
         <v>117</v>
       </c>
       <c r="P3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
         <v>3</v>
@@ -2983,11 +2983,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3011,41 +3011,41 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25-24</t>
+          <t>30-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>4-10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M4" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P4" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>6</v>
@@ -3054,11 +3054,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3072,51 +3072,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>0.553</v>
+        <v>0.551</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30-17</t>
+          <t>25-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P5" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="M6" t="n">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -3184,10 +3184,10 @@
         <v>106</v>
       </c>
       <c r="P6" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q6" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R6" t="n">
         <v>14</v>
@@ -3218,17 +3218,17 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
         <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.727</v>
+        <v>0.731</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>35-12</t>
+          <t>36-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -3259,7 +3259,7 @@
         <v>117</v>
       </c>
       <c r="P7" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q7" t="n">
         <v>8</v>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - c</t>
+          <t xml:space="preserve"> - e</t>
         </is>
       </c>
     </row>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -3371,14 +3371,14 @@
         <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20-27</t>
+          <t>20-28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3388,19 +3388,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="M9" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="M10" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -3484,7 +3484,7 @@
         <v>116</v>
       </c>
       <c r="P10" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q10" t="n">
         <v>-5</v>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="M11" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -3668,17 +3668,17 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.636</v>
+        <v>0.641</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>31-16</t>
+          <t>32-16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3688,25 +3688,25 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>W 7</t>
+          <t>W 8</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P13" t="n">
         <v>117</v>
@@ -3888,14 +3888,14 @@
         <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>0.273</v>
+        <v>0.269</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-36</t>
+          <t>11-37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3910,14 +3910,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 7</t>
+          <t>L 8</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="M16" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -3926,13 +3926,13 @@
         <v>117</v>
       </c>
       <c r="P16" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q16" t="n">
         <v>-8</v>
       </c>
       <c r="R16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -4248,17 +4248,17 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F21" t="n">
         <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>0.26</v>
+        <v>0.269</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>12-35</t>
+          <t>13-35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -4273,14 +4273,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>41</v>
+        <v>40.5</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>29.5</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4295,7 +4295,7 @@
         <v>-10</v>
       </c>
       <c r="R21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4361,13 +4361,13 @@
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P22" t="n">
         <v>116</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
         <v>5</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
@@ -4465,13 +4465,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F24" t="n">
         <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.526</v>
+        <v>0.532</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -4485,19 +4485,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L24" t="n">
         <v>15.5</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -4536,45 +4536,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n">
         <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>0.519</v>
+        <v>0.526</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24-23</t>
+          <t>25-23</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>8-7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>16</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P25" t="n">
         <v>118</v>
@@ -4610,19 +4610,19 @@
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
-        <v>0.224</v>
+        <v>0.221</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-35</t>
+          <t>11-36</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>2-13</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4632,14 +4632,14 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="M26" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -4648,7 +4648,7 @@
         <v>113</v>
       </c>
       <c r="P26" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q26" t="n">
         <v>-12</v>
@@ -4685,14 +4685,14 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.766</v>
+        <v>0.756</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>34-14</t>
+          <t>34-15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4702,16 +4702,16 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>10-0</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>W 11</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4757,17 +4757,17 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F28" t="n">
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.618</v>
+        <v>0.623</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25-22</t>
+          <t>26-22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4777,31 +4777,31 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M28" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P28" t="n">
         <v>110</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
         <v>5</v>
@@ -4835,10 +4835,10 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G29" t="n">
-        <v>0.329</v>
+        <v>0.325</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="M29" t="n">
         <v>33.5</v>
@@ -4873,10 +4873,10 @@
         <v>115</v>
       </c>
       <c r="P29" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q29" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R29" t="n">
         <v>11</v>
@@ -4910,14 +4910,14 @@
         <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G30" t="n">
-        <v>0.325</v>
+        <v>0.321</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>16-32</t>
+          <t>16-33</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4932,11 +4932,11 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>L 7</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="M30" t="n">
         <v>34</v>
@@ -4985,10 +4985,10 @@
         <v>24</v>
       </c>
       <c r="F31" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G31" t="n">
-        <v>0.316</v>
+        <v>0.312</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -5007,11 +5007,11 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="M31" t="n">
         <v>34.5</v>
@@ -5020,7 +5020,7 @@
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P31" t="n">
         <v>119</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,97 +430,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>conference</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>division</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>wins</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>losses</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>win_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>conf_record</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>div_record</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>last10</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>streak</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>games_back</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>div_games_back</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>div_rank</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>pts_per_game</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>opp_pts_per_game</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>pt_diff_per_game</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>clinch</t>
         </is>
@@ -537,14 +549,14 @@
         <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>0.731</v>
+        <v>0.722</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>36-12</t>
+          <t>36-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -554,12 +566,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -575,7 +587,7 @@
         <v>117</v>
       </c>
       <c r="P2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q2" t="n">
         <v>8</v>
@@ -609,22 +621,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.675</v>
+        <v>0.679</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>33-15</t>
+          <t>34-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -634,11 +646,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -684,17 +696,17 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F4" t="n">
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.641</v>
+        <v>0.646</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>32-16</t>
+          <t>33-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -709,11 +721,11 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>2.5</v>
@@ -728,7 +740,7 @@
         <v>110</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
         <v>3</v>
@@ -759,45 +771,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>0.623</v>
+        <v>0.633</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30-18</t>
+          <t>31-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="M5" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P5" t="n">
         <v>115</v>
@@ -837,14 +849,14 @@
         <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>0.577</v>
+        <v>0.57</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>26-22</t>
+          <t>26-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,12 +866,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -872,7 +884,7 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P6" t="n">
         <v>116</v>
@@ -908,42 +920,42 @@
         <v>43</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30-17</t>
+          <t>30-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L7" t="n">
         <v>13.5</v>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P7" t="n">
         <v>112</v>
@@ -979,10 +991,10 @@
         <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>0.551</v>
+        <v>0.544</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1001,14 +1013,14 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
@@ -1047,13 +1059,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" t="n">
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>0.538</v>
+        <v>0.544</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1072,14 +1084,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -1118,17 +1130,17 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.532</v>
+        <v>0.544</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>25-25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1138,19 +1150,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1218,10 +1230,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
@@ -1260,13 +1272,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
         <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>0.39</v>
+        <v>0.397</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1280,19 +1292,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="M12" t="n">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1338,10 +1350,10 @@
         <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0.377</v>
+        <v>0.372</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1355,12 +1367,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>L 7</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1392,11 +1404,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1406,55 +1418,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
         <v>59</v>
       </c>
       <c r="G14" t="n">
-        <v>0.234</v>
+        <v>0.244</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14-34</t>
+          <t>13-34</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>3-12</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="M14" t="n">
-        <v>38.5</v>
+        <v>34</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="P14" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="R14" t="n">
         <v>13</v>
@@ -1467,11 +1479,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1481,31 +1493,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>0.234</v>
+        <v>0.231</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12-34</t>
+          <t>14-35</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1517,19 +1529,19 @@
         <v>38.5</v>
       </c>
       <c r="M15" t="n">
-        <v>34</v>
+        <v>38.5</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="P15" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="Q15" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="R15" t="n">
         <v>14</v>
@@ -1563,14 +1575,14 @@
         <v>17</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G16" t="n">
-        <v>0.221</v>
+        <v>0.218</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-36</t>
+          <t>11-37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1585,7 +1597,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1635,22 +1647,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.792</v>
+        <v>0.795</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>38-9</t>
+          <t>39-9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11-3</t>
+          <t>12-3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1660,7 +1672,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1676,10 +1688,10 @@
         <v>119</v>
       </c>
       <c r="P17" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -1710,13 +1722,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" t="n">
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.756</v>
+        <v>0.759</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1735,7 +1747,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1767,11 +1779,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1610612747</v>
+        <v>1610612743</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Nuggets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1781,72 +1793,72 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Northwest</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.649</v>
+        <v>0.646</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>30-17</t>
+          <t>33-16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8-7</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 9</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
+        <v>122</v>
+      </c>
+      <c r="P19" t="n">
         <v>117</v>
       </c>
-      <c r="P19" t="n">
-        <v>115</v>
-      </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
         <v>3</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - p</t>
+          <t xml:space="preserve"> - x</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1610612743</v>
+        <v>1610612747</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Lakers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1856,7 +1868,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Northwest</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1870,48 +1882,48 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>32-16</t>
+          <t>30-18</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>8-7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>W 8</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="P20" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>4</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - x</t>
+          <t xml:space="preserve"> - p</t>
         </is>
       </c>
     </row>
@@ -1935,17 +1947,17 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
         <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>0.623</v>
+        <v>0.628</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>26-22</t>
+          <t>27-22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1955,12 +1967,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>W 6</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -2013,10 +2025,10 @@
         <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>0.597</v>
+        <v>0.59</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2035,26 +2047,26 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P22" t="n">
         <v>114</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
         <v>6</v>
@@ -2081,13 +2093,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" t="n">
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.545</v>
+        <v>0.551</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2101,19 +2113,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>19</v>
       </c>
       <c r="M23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -2125,7 +2137,7 @@
         <v>111</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
         <v>7</v>
@@ -2134,11 +2146,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2148,7 +2160,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Northwest</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2162,41 +2174,41 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>27-21</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="M24" t="n">
-        <v>21.5</v>
+        <v>10</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P24" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>8</v>
@@ -2205,11 +2217,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2219,55 +2231,55 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Northwest</t>
         </is>
       </c>
       <c r="E25" t="n">
+        <v>40</v>
+      </c>
+      <c r="F25" t="n">
         <v>39</v>
-      </c>
-      <c r="F25" t="n">
-        <v>38</v>
       </c>
       <c r="G25" t="n">
         <v>0.506</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22-25</t>
+          <t>27-22</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="M25" t="n">
-        <v>11</v>
+        <v>22.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P25" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R25" t="n">
         <v>9</v>
@@ -2297,14 +2309,14 @@
         <v>36</v>
       </c>
       <c r="F26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G26" t="n">
-        <v>0.468</v>
+        <v>0.462</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23-24</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2314,16 +2326,16 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M26" t="n">
         <v>14</v>
@@ -2347,11 +2359,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2368,19 +2380,19 @@
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G27" t="n">
-        <v>0.325</v>
+        <v>0.321</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>19-30</t>
+          <t>14-34</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2390,26 +2402,26 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M27" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P27" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q27" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R27" t="n">
         <v>11</v>
@@ -2443,10 +2455,10 @@
         <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G28" t="n">
-        <v>0.321</v>
+        <v>0.316</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2460,19 +2472,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 7</t>
+          <t>L 8</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
       <c r="M28" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -2497,11 +2509,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2515,51 +2527,51 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G29" t="n">
-        <v>0.312</v>
+        <v>0.316</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>13-34</t>
+          <t>19-30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M29" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q29" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R29" t="n">
         <v>13</v>
@@ -2593,33 +2605,33 @@
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G30" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>13-35</t>
+          <t>13-36</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3-10</t>
+          <t>3-11</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="M30" t="n">
         <v>29.5</v>
@@ -2668,19 +2680,19 @@
         <v>21</v>
       </c>
       <c r="F31" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G31" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11-37</t>
+          <t>11-38</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1-14</t>
+          <t>1-15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2690,14 +2702,14 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 8</t>
+          <t>L 9</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="M31" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2709,7 +2721,7 @@
         <v>126</v>
       </c>
       <c r="Q31" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R31" t="n">
         <v>15</v>
@@ -2735,97 +2747,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>team_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>conference</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>division</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>wins</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>losses</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>win_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>conf_record</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>div_record</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>last10</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>streak</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>games_back</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>div_games_back</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>div_rank</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>pts_per_game</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>opp_pts_per_game</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>pt_diff_per_game</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>clinch</t>
         </is>
@@ -2851,22 +2863,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
         <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.675</v>
+        <v>0.679</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>33-15</t>
+          <t>34-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2876,11 +2888,11 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2926,17 +2938,17 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
         <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.641</v>
+        <v>0.646</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>32-16</t>
+          <t>33-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2951,11 +2963,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>2.5</v>
@@ -2970,7 +2982,7 @@
         <v>110</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
         <v>3</v>
@@ -3004,42 +3016,42 @@
         <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>30-17</t>
+          <t>30-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>13.5</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P4" t="n">
         <v>112</v>
@@ -3075,10 +3087,10 @@
         <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>0.551</v>
+        <v>0.544</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3097,14 +3109,14 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L5" t="n">
         <v>14</v>
       </c>
       <c r="M5" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -3143,17 +3155,17 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" t="n">
         <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>0.234</v>
+        <v>0.244</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12-34</t>
+          <t>13-34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3163,16 +3175,16 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="M6" t="n">
         <v>34</v>
@@ -3190,7 +3202,7 @@
         <v>-10</v>
       </c>
       <c r="R6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -3221,14 +3233,14 @@
         <v>57</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.731</v>
+        <v>0.722</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>36-12</t>
+          <t>36-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3238,12 +3250,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -3259,7 +3271,7 @@
         <v>117</v>
       </c>
       <c r="P7" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q7" t="n">
         <v>8</v>
@@ -3293,45 +3305,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.623</v>
+        <v>0.633</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30-18</t>
+          <t>31-18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P8" t="n">
         <v>115</v>
@@ -3368,13 +3380,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9" t="n">
         <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>0.39</v>
+        <v>0.397</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3388,19 +3400,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="M9" t="n">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -3446,10 +3458,10 @@
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>0.377</v>
+        <v>0.372</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3463,12 +3475,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>L 7</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -3521,19 +3533,19 @@
         <v>18</v>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>0.234</v>
+        <v>0.231</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14-34</t>
+          <t>14-35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4-10</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3543,7 +3555,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -3565,7 +3577,7 @@
         <v>-8</v>
       </c>
       <c r="R11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -3593,22 +3605,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.792</v>
+        <v>0.795</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>38-9</t>
+          <t>39-9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11-3</t>
+          <t>12-3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3618,7 +3630,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 5</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -3634,10 +3646,10 @@
         <v>119</v>
       </c>
       <c r="P12" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -3668,22 +3680,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.641</v>
+        <v>0.646</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>32-16</t>
+          <t>33-16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3693,7 +3705,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>W 8</t>
+          <t>W 9</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -3715,7 +3727,7 @@
         <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -3746,10 +3758,10 @@
         <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G14" t="n">
-        <v>0.597</v>
+        <v>0.59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3768,26 +3780,26 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P14" t="n">
         <v>114</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
         <v>6</v>
@@ -3817,42 +3829,42 @@
         <v>40</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>0.513</v>
+        <v>0.506</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>27-21</t>
+          <t>27-22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="M15" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P15" t="n">
         <v>116</v>
@@ -3861,7 +3873,7 @@
         <v>-1</v>
       </c>
       <c r="R15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S15" t="inlineStr"/>
     </row>
@@ -3888,19 +3900,19 @@
         <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-37</t>
+          <t>11-38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1-14</t>
+          <t>1-15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3910,14 +3922,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 8</t>
+          <t>L 9</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="M16" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -3929,7 +3941,7 @@
         <v>126</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R16" t="n">
         <v>15</v>
@@ -3963,14 +3975,14 @@
         <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" t="n">
-        <v>0.649</v>
+        <v>0.641</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30-17</t>
+          <t>30-18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3980,16 +3992,16 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -4004,10 +4016,10 @@
         <v>115</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -4035,13 +4047,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F18" t="n">
         <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>0.545</v>
+        <v>0.551</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -4055,19 +4067,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>19</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -4079,7 +4091,7 @@
         <v>111</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>7</v>
@@ -4106,39 +4118,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
         <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>0.506</v>
+        <v>0.513</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22-25</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L19" t="n">
         <v>22</v>
       </c>
       <c r="M19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -4153,7 +4165,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S19" t="inlineStr"/>
     </row>
@@ -4180,14 +4192,14 @@
         <v>36</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>0.468</v>
+        <v>0.462</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23-24</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4197,16 +4209,16 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 4</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M20" t="n">
         <v>14</v>
@@ -4251,33 +4263,33 @@
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G21" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>13-35</t>
+          <t>13-36</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3-10</t>
+          <t>3-11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="M21" t="n">
         <v>29.5</v>
@@ -4326,14 +4338,14 @@
         <v>45</v>
       </c>
       <c r="F22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>0.577</v>
+        <v>0.57</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>26-22</t>
+          <t>26-23</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4343,12 +4355,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -4361,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P22" t="n">
         <v>116</v>
@@ -4394,13 +4406,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" t="n">
         <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>0.538</v>
+        <v>0.544</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -4419,14 +4431,14 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -4465,17 +4477,17 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F24" t="n">
         <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.532</v>
+        <v>0.544</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>25-25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -4485,19 +4497,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
         <v>3</v>
@@ -4565,10 +4577,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
@@ -4610,14 +4622,14 @@
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G26" t="n">
-        <v>0.221</v>
+        <v>0.218</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-36</t>
+          <t>11-37</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4632,7 +4644,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -4682,13 +4694,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F27" t="n">
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.756</v>
+        <v>0.759</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -4707,7 +4719,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -4757,17 +4769,17 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F28" t="n">
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.623</v>
+        <v>0.628</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>26-22</t>
+          <t>27-22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4777,12 +4789,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>W 6</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -4814,11 +4826,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4835,19 +4847,19 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G29" t="n">
-        <v>0.325</v>
+        <v>0.321</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19-30</t>
+          <t>14-34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4857,26 +4869,26 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M29" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P29" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q29" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R29" t="n">
         <v>11</v>
@@ -4910,10 +4922,10 @@
         <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G30" t="n">
-        <v>0.321</v>
+        <v>0.316</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4927,19 +4939,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 7</t>
+          <t>L 8</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
       <c r="M30" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -4964,11 +4976,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4982,51 +4994,51 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G31" t="n">
-        <v>0.312</v>
+        <v>0.316</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13-34</t>
+          <t>19-30</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 5</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="M31" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P31" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q31" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R31" t="n">
         <v>13</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -546,22 +546,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
         <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>0.722</v>
+        <v>0.725</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>36-13</t>
+          <t>37-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>11-4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -584,7 +584,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P2" t="n">
         <v>110</v>
@@ -621,36 +621,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>0.679</v>
+        <v>0.675</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>34-15</t>
+          <t>35-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.646</v>
+        <v>0.65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>33-16</t>
+          <t>34-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12-3</t>
+          <t>13-3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -721,14 +721,14 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -771,17 +771,17 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>0.633</v>
+        <v>0.638</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>31-18</t>
+          <t>32-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -828,11 +828,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -842,52 +842,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>0.57</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>26-23</t>
+          <t>32-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P6" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
@@ -899,11 +899,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,55 +913,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
         <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>0.551</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30-18</t>
+          <t>26-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>118</v>
+      </c>
+      <c r="P7" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>114</v>
-      </c>
-      <c r="P7" t="n">
-        <v>112</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>6</v>
@@ -970,11 +970,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -984,17 +984,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
         <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>0.544</v>
+        <v>0.55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1013,23 +1013,23 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>10.5</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>116</v>
       </c>
       <c r="P8" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1041,11 +1041,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1055,55 +1055,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>43</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>0.544</v>
+        <v>0.538</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25-24</t>
+          <t>25-25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>116</v>
       </c>
       <c r="P9" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R9" t="n">
         <v>8</v>
@@ -1112,11 +1112,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1133,10 +1133,10 @@
         <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>0.544</v>
+        <v>0.538</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1145,21 +1145,21 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9-8</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
@@ -1168,13 +1168,13 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P10" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
         <v>9</v>
@@ -1204,14 +1204,14 @@
         <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>0.526</v>
+        <v>0.513</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25-23</t>
+          <t>25-25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1226,23 +1226,23 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P11" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q11" t="n">
         <v>2</v>
@@ -1275,36 +1275,36 @@
         <v>31</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>0.397</v>
+        <v>0.388</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20-28</t>
+          <t>20-30</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="M12" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1347,17 +1347,17 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F13" t="n">
         <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0.372</v>
+        <v>0.388</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-31</t>
+          <t>19-31</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,19 +1367,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>L 7</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="M13" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -1388,7 +1388,7 @@
         <v>116</v>
       </c>
       <c r="P13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q13" t="n">
         <v>-5</v>
@@ -1422,17 +1422,17 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>0.244</v>
+        <v>0.25</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13-34</t>
+          <t>14-35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1442,16 +1442,16 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M14" t="n">
         <v>34</v>
@@ -1497,17 +1497,17 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>0.231</v>
+        <v>0.238</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14-35</t>
+          <t>15-35</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1517,19 +1517,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="M15" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
@@ -1538,7 +1538,7 @@
         <v>113</v>
       </c>
       <c r="P15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q15" t="n">
         <v>-8</v>
@@ -1575,14 +1575,14 @@
         <v>17</v>
       </c>
       <c r="F16" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>0.218</v>
+        <v>0.213</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-37</t>
+          <t>11-39</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1597,14 +1597,14 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>L 8</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>39.5</v>
+        <v>41</v>
       </c>
       <c r="M16" t="n">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -1647,17 +1647,17 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.795</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>39-9</t>
+          <t>41-9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>W 7</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1688,7 +1688,7 @@
         <v>119</v>
       </c>
       <c r="P17" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q17" t="n">
         <v>12</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - nw</t>
+          <t xml:space="preserve"> - w</t>
         </is>
       </c>
     </row>
@@ -1722,17 +1722,17 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F18" t="n">
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.759</v>
+        <v>0.763</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>34-15</t>
+          <t>35-15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1747,11 +1747,11 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1797,17 +1797,17 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" t="n">
         <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.646</v>
+        <v>0.65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>33-16</t>
+          <t>34-16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1817,19 +1817,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>10-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 9</t>
+          <t>W 10</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N19" t="n">
         <v>2</v>
@@ -1872,36 +1872,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G20" t="n">
-        <v>0.641</v>
+        <v>0.638</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30-18</t>
+          <t>31-19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8-7</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P20" t="n">
         <v>115</v>
@@ -1947,17 +1947,17 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F21" t="n">
         <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>0.628</v>
+        <v>0.638</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27-22</t>
+          <t>28-22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1972,14 +1972,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>W 6</t>
+          <t>W 8</t>
         </is>
       </c>
       <c r="L21" t="n">
         <v>13</v>
       </c>
       <c r="M21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="N21" t="n">
         <v>2</v>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0.59</v>
+        <v>0.588</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2042,25 +2042,25 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P22" t="n">
         <v>114</v>
@@ -2071,7 +2071,11 @@
       <c r="R22" t="n">
         <v>6</v>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2093,17 +2097,17 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>0.551</v>
+        <v>0.55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>27-21</t>
+          <t>28-22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2113,7 +2117,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2122,7 +2126,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M23" t="n">
         <v>7</v>
@@ -2137,7 +2141,7 @@
         <v>111</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>7</v>
@@ -2164,17 +2168,17 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
         <v>0.513</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>24-26</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2184,16 +2188,16 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M24" t="n">
         <v>10</v>
@@ -2238,14 +2242,14 @@
         <v>40</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>0.506</v>
+        <v>0.5</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>27-22</t>
+          <t>27-23</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2255,25 +2259,25 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="M25" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P25" t="n">
         <v>116</v>
@@ -2306,36 +2310,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F26" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>24-26</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M26" t="n">
         <v>14</v>
@@ -2359,11 +2363,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2377,22 +2381,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F27" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G27" t="n">
-        <v>0.321</v>
+        <v>0.325</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14-34</t>
+          <t>17-33</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2406,22 +2410,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M27" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P27" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q27" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="R27" t="n">
         <v>11</v>
@@ -2434,11 +2438,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2455,36 +2459,36 @@
         <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G28" t="n">
-        <v>0.316</v>
+        <v>0.313</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16-33</t>
+          <t>19-31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 8</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="M28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -2493,7 +2497,7 @@
         <v>115</v>
       </c>
       <c r="P28" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q28" t="n">
         <v>-5</v>
@@ -2509,11 +2513,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2530,48 +2534,48 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G29" t="n">
-        <v>0.316</v>
+        <v>0.313</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19-30</t>
+          <t>14-36</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="M29" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P29" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q29" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R29" t="n">
         <v>13</v>
@@ -2605,19 +2609,19 @@
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G30" t="n">
-        <v>0.266</v>
+        <v>0.263</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>13-36</t>
+          <t>13-37</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3-11</t>
+          <t>3-12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2627,14 +2631,14 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>41.5</v>
+        <v>43</v>
       </c>
       <c r="M30" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
@@ -2680,14 +2684,14 @@
         <v>21</v>
       </c>
       <c r="F31" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G31" t="n">
-        <v>0.266</v>
+        <v>0.263</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11-38</t>
+          <t>11-39</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2697,19 +2701,19 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 9</t>
+          <t>L 10</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>41.5</v>
+        <v>43</v>
       </c>
       <c r="M31" t="n">
-        <v>41.5</v>
+        <v>43</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2863,36 +2867,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.679</v>
+        <v>0.675</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>34-15</t>
+          <t>35-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2938,22 +2942,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
         <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.646</v>
+        <v>0.65</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>33-16</t>
+          <t>34-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12-3</t>
+          <t>13-3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2963,14 +2967,14 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L3" t="n">
         <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -3013,17 +3017,17 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
         <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>0.551</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>30-18</t>
+          <t>32-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3033,34 +3037,34 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P4" t="n">
         <v>112</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S4" t="inlineStr"/>
     </row>
@@ -3087,10 +3091,10 @@
         <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.544</v>
+        <v>0.538</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3104,19 +3108,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -3125,13 +3129,13 @@
         <v>116</v>
       </c>
       <c r="P5" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S5" t="inlineStr"/>
     </row>
@@ -3155,17 +3159,17 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0.244</v>
+        <v>0.25</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13-34</t>
+          <t>14-35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3175,16 +3179,16 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
         <v>34</v>
@@ -3230,22 +3234,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
         <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.722</v>
+        <v>0.725</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>36-13</t>
+          <t>37-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>11-4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3255,7 +3259,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -3268,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P7" t="n">
         <v>110</v>
@@ -3305,17 +3309,17 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.633</v>
+        <v>0.638</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>31-18</t>
+          <t>32-18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3330,7 +3334,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>W 4</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -3383,36 +3387,36 @@
         <v>31</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>0.397</v>
+        <v>0.388</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20-28</t>
+          <t>20-30</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -3455,17 +3459,17 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
         <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>0.372</v>
+        <v>0.388</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-31</t>
+          <t>19-31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3475,19 +3479,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 7</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="M10" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -3496,7 +3500,7 @@
         <v>116</v>
       </c>
       <c r="P10" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q10" t="n">
         <v>-5</v>
@@ -3530,17 +3534,17 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>0.231</v>
+        <v>0.238</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14-35</t>
+          <t>15-35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3550,19 +3554,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="M11" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -3571,7 +3575,7 @@
         <v>113</v>
       </c>
       <c r="P11" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q11" t="n">
         <v>-8</v>
@@ -3605,17 +3609,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
         <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.795</v>
+        <v>0.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>39-9</t>
+          <t>41-9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3630,7 +3634,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>W 5</t>
+          <t>W 7</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -3646,7 +3650,7 @@
         <v>119</v>
       </c>
       <c r="P12" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q12" t="n">
         <v>12</v>
@@ -3656,7 +3660,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - nw</t>
+          <t xml:space="preserve"> - w</t>
         </is>
       </c>
     </row>
@@ -3680,17 +3684,17 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.646</v>
+        <v>0.65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>33-16</t>
+          <t>34-16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3700,19 +3704,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>10-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>W 9</t>
+          <t>W 10</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -3755,13 +3759,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>0.59</v>
+        <v>0.588</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3775,25 +3779,25 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P14" t="n">
         <v>114</v>
@@ -3804,7 +3808,11 @@
       <c r="R14" t="n">
         <v>6</v>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3829,14 +3837,14 @@
         <v>40</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>0.506</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>27-22</t>
+          <t>27-23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3846,25 +3854,25 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="M15" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P15" t="n">
         <v>116</v>
@@ -3900,14 +3908,14 @@
         <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G16" t="n">
-        <v>0.266</v>
+        <v>0.263</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-38</t>
+          <t>11-39</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3917,19 +3925,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 9</t>
+          <t>L 10</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.5</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>41.5</v>
+        <v>43</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -3972,36 +3980,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.641</v>
+        <v>0.638</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30-18</t>
+          <t>31-19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8-7</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -4010,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P17" t="n">
         <v>115</v>
@@ -4047,17 +4055,17 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>0.551</v>
+        <v>0.55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>27-21</t>
+          <t>28-22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4067,7 +4075,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -4076,7 +4084,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M18" t="n">
         <v>7</v>
@@ -4091,7 +4099,7 @@
         <v>111</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>7</v>
@@ -4118,17 +4126,17 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
         <v>0.513</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>24-26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4138,16 +4146,16 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M19" t="n">
         <v>10</v>
@@ -4189,36 +4197,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>24-26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>L 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M20" t="n">
         <v>14</v>
@@ -4263,19 +4271,19 @@
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
-        <v>0.266</v>
+        <v>0.263</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>13-36</t>
+          <t>13-37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3-11</t>
+          <t>3-12</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4285,14 +4293,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>41.5</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4338,14 +4346,14 @@
         <v>45</v>
       </c>
       <c r="F22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G22" t="n">
-        <v>0.57</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>26-23</t>
+          <t>26-24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4360,11 +4368,11 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4382,17 +4390,17 @@
         <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4406,27 +4414,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F23" t="n">
         <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>0.544</v>
+        <v>0.55</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25-24</t>
+          <t>25-25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4438,7 +4446,7 @@
         <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -4447,23 +4455,23 @@
         <v>116</v>
       </c>
       <c r="P23" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4480,10 +4488,10 @@
         <v>43</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.544</v>
+        <v>0.538</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -4492,21 +4500,21 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9-8</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>W 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M24" t="n">
         <v>2</v>
@@ -4515,13 +4523,13 @@
         <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P24" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
         <v>9</v>
@@ -4551,14 +4559,14 @@
         <v>41</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>0.526</v>
+        <v>0.513</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25-23</t>
+          <t>25-25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4573,23 +4581,23 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P25" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q25" t="n">
         <v>2</v>
@@ -4622,14 +4630,14 @@
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G26" t="n">
-        <v>0.218</v>
+        <v>0.213</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-37</t>
+          <t>11-39</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4644,14 +4652,14 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>L 8</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>39.5</v>
+        <v>41</v>
       </c>
       <c r="M26" t="n">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -4694,17 +4702,17 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F27" t="n">
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.759</v>
+        <v>0.763</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>34-15</t>
+          <t>35-15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4719,11 +4727,11 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4769,17 +4777,17 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F28" t="n">
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.628</v>
+        <v>0.638</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>27-22</t>
+          <t>28-22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4794,14 +4802,14 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>W 6</t>
+          <t>W 8</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>13</v>
       </c>
       <c r="M28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="N28" t="n">
         <v>2</v>
@@ -4826,11 +4834,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4844,22 +4852,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G29" t="n">
-        <v>0.321</v>
+        <v>0.325</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14-34</t>
+          <t>17-33</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4873,22 +4881,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M29" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q29" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="R29" t="n">
         <v>11</v>
@@ -4901,11 +4909,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4922,36 +4930,36 @@
         <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G30" t="n">
-        <v>0.316</v>
+        <v>0.313</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>16-33</t>
+          <t>19-31</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 8</t>
+          <t>L 6</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="M30" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N30" t="n">
         <v>4</v>
@@ -4960,7 +4968,7 @@
         <v>115</v>
       </c>
       <c r="P30" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" t="n">
         <v>-5</v>
@@ -4976,11 +4984,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4997,48 +5005,48 @@
         <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G31" t="n">
-        <v>0.316</v>
+        <v>0.313</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>19-30</t>
+          <t>14-36</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>4-11</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 5</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P31" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q31" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R31" t="n">
         <v>13</v>

--- a/nba/public/data/nba_standings.xlsx
+++ b/nba/public/data/nba_standings.xlsx
@@ -546,32 +546,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
         <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>0.725</v>
+        <v>0.732</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>37-13</t>
+          <t>39-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11-4</t>
+          <t>12-4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -621,17 +621,17 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
         <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>0.675</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>35-16</t>
+          <t>36-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -672,7 +672,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - x</t>
+          <t xml:space="preserve"> - a</t>
         </is>
       </c>
     </row>
@@ -696,45 +696,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.65</v>
+        <v>0.646</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>34-16</t>
+          <t>35-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13-3</t>
+          <t>14-3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P4" t="n">
         <v>110</v>
@@ -771,17 +771,17 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>0.638</v>
+        <v>0.634</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>32-18</t>
+          <t>33-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -791,19 +791,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
@@ -846,22 +846,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>32-18</t>
+          <t>33-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>5-12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -871,14 +871,14 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
         <v>3</v>
@@ -895,7 +895,11 @@
       <c r="R6" t="n">
         <v>5</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -917,36 +921,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>26-24</t>
+          <t>27-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -961,20 +965,24 @@
         <v>116</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>6</v>
       </c>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - se</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -984,26 +992,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Atlantic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>0.55</v>
+        <v>0.549</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25-25</t>
+          <t>27-25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9-8</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1013,23 +1021,23 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>116</v>
       </c>
       <c r="P8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1041,11 +1049,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1055,55 +1063,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Atlantic</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
         <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>0.538</v>
+        <v>0.549</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25-25</t>
+          <t>26-26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L9" t="n">
         <v>15</v>
       </c>
       <c r="M9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
         <v>116</v>
       </c>
       <c r="P9" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>8</v>
@@ -1130,17 +1138,17 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>0.538</v>
+        <v>0.537</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>25-25</t>
+          <t>26-26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1150,16 +1158,16 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
@@ -1201,45 +1209,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>0.513</v>
+        <v>0.524</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25-25</t>
+          <t>27-25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8-7</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L11" t="n">
         <v>17</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P11" t="n">
         <v>119</v>
@@ -1272,17 +1280,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>0.388</v>
+        <v>0.39</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20-30</t>
+          <t>21-31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1292,19 +1300,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1350,14 +1358,14 @@
         <v>31</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>0.388</v>
+        <v>0.378</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>19-31</t>
+          <t>19-32</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1367,19 +1375,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N13" t="n">
         <v>4</v>
@@ -1388,7 +1396,7 @@
         <v>116</v>
       </c>
       <c r="P13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q13" t="n">
         <v>-5</v>
@@ -1425,19 +1433,19 @@
         <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>0.25</v>
+        <v>0.244</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14-35</t>
+          <t>14-37</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>3-13</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1447,14 +1455,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N14" t="n">
         <v>5</v>
@@ -1500,42 +1508,42 @@
         <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G15" t="n">
-        <v>0.238</v>
+        <v>0.232</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>15-35</t>
+          <t>15-37</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>4-12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N15" t="n">
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P15" t="n">
         <v>120</v>
@@ -1575,36 +1583,36 @@
         <v>17</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>0.213</v>
+        <v>0.207</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-39</t>
+          <t>11-41</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2-13</t>
+          <t>2-14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 8</t>
+          <t>L 10</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
@@ -1650,29 +1658,29 @@
         <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>41-9</t>
+          <t>41-11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12-3</t>
+          <t>12-4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 7</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1688,10 +1696,10 @@
         <v>119</v>
       </c>
       <c r="P17" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -1722,36 +1730,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>0.763</v>
+        <v>0.756</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>35-15</t>
+          <t>36-16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12-3</t>
+          <t>13-3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1763,7 +1771,7 @@
         <v>120</v>
       </c>
       <c r="P18" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q18" t="n">
         <v>8</v>
@@ -1797,22 +1805,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
         <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.65</v>
+        <v>0.659</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>34-16</t>
+          <t>36-16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1822,14 +1830,14 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>W 10</t>
+          <t>W 12</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
         <v>2</v>
@@ -1872,36 +1880,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F20" t="n">
         <v>29</v>
       </c>
       <c r="G20" t="n">
-        <v>0.638</v>
+        <v>0.646</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>31-19</t>
+          <t>33-19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1916,7 +1924,7 @@
         <v>115</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>4</v>
@@ -1947,36 +1955,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>0.638</v>
+        <v>0.634</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>28-22</t>
+          <t>29-23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>W 8</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M21" t="n">
         <v>10</v>
@@ -2022,17 +2030,17 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F22" t="n">
         <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0.588</v>
+        <v>0.598</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>29-21</t>
+          <t>31-21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2042,19 +2050,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
@@ -2063,7 +2071,7 @@
         <v>118</v>
       </c>
       <c r="P22" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q22" t="n">
         <v>3</v>
@@ -2097,22 +2105,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>0.55</v>
+        <v>0.549</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>28-22</t>
+          <t>29-23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2126,10 +2134,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -2150,11 +2158,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2164,26 +2172,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Northwest</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>0.513</v>
+        <v>0.512</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24-26</t>
+          <t>29-23</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2193,26 +2201,26 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P24" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>8</v>
@@ -2221,11 +2229,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2235,26 +2243,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Northwest</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
         <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.512</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>27-23</t>
+          <t>25-27</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2264,26 +2272,26 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M25" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P25" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>9</v>
@@ -2313,36 +2321,36 @@
         <v>37</v>
       </c>
       <c r="F26" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G26" t="n">
-        <v>0.463</v>
+        <v>0.451</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>24-26</t>
+          <t>24-28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L26" t="n">
         <v>27</v>
       </c>
       <c r="M26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
@@ -2354,7 +2362,7 @@
         <v>115</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R26" t="n">
         <v>10</v>
@@ -2384,14 +2392,14 @@
         <v>26</v>
       </c>
       <c r="F27" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G27" t="n">
-        <v>0.325</v>
+        <v>0.317</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17-33</t>
+          <t>17-34</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2401,31 +2409,31 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>38</v>
       </c>
       <c r="M27" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N27" t="n">
         <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P27" t="n">
         <v>120</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R27" t="n">
         <v>11</v>
@@ -2438,11 +2446,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2456,36 +2464,36 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F28" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G28" t="n">
-        <v>0.313</v>
+        <v>0.317</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>19-31</t>
+          <t>14-37</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>4-12</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M28" t="n">
         <v>36</v>
@@ -2494,13 +2502,13 @@
         <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P28" t="n">
         <v>120</v>
       </c>
       <c r="Q28" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R28" t="n">
         <v>12</v>
@@ -2513,11 +2521,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2534,45 +2542,45 @@
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G29" t="n">
-        <v>0.313</v>
+        <v>0.305</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14-36</t>
+          <t>19-33</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 8</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>39</v>
       </c>
       <c r="M29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N29" t="n">
         <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q29" t="n">
         <v>-6</v>
@@ -2606,22 +2614,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
-        <v>0.263</v>
+        <v>0.268</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>13-37</t>
+          <t>14-38</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>4-12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2631,14 +2639,14 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M30" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
@@ -2681,17 +2689,17 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G31" t="n">
-        <v>0.263</v>
+        <v>0.268</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11-39</t>
+          <t>12-40</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2701,31 +2709,31 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 10</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" t="n">
         <v>126</v>
       </c>
       <c r="Q31" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R31" t="n">
         <v>15</v>
@@ -2867,17 +2875,17 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.675</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>35-16</t>
+          <t>36-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2887,12 +2895,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -2918,7 +2926,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - x</t>
+          <t xml:space="preserve"> - a</t>
         </is>
       </c>
     </row>
@@ -2942,45 +2950,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.65</v>
+        <v>0.646</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>34-16</t>
+          <t>35-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13-3</t>
+          <t>14-3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P3" t="n">
         <v>110</v>
@@ -3017,22 +3025,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>32-18</t>
+          <t>33-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>5-12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3042,14 +3050,14 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -3066,7 +3074,11 @@
       <c r="R4" t="n">
         <v>5</v>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - x</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3088,17 +3100,17 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
         <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.538</v>
+        <v>0.549</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25-25</t>
+          <t>27-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3108,12 +3120,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L 3</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -3132,10 +3144,10 @@
         <v>116</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S5" t="inlineStr"/>
     </row>
@@ -3162,19 +3174,19 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>0.25</v>
+        <v>0.244</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-35</t>
+          <t>14-37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>3-13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3184,14 +3196,14 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -3234,32 +3246,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
         <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.725</v>
+        <v>0.732</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>37-13</t>
+          <t>39-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11-4</t>
+          <t>12-4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -3309,17 +3321,17 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>0.638</v>
+        <v>0.634</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32-18</t>
+          <t>33-19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3329,19 +3341,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -3384,17 +3396,17 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>0.388</v>
+        <v>0.39</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20-30</t>
+          <t>21-31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3404,19 +3416,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -3462,14 +3474,14 @@
         <v>31</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>0.388</v>
+        <v>0.378</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>19-31</t>
+          <t>19-32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3479,19 +3491,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -3500,7 +3512,7 @@
         <v>116</v>
       </c>
       <c r="P10" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q10" t="n">
         <v>-5</v>
@@ -3537,42 +3549,42 @@
         <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>0.238</v>
+        <v>0.232</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15-35</t>
+          <t>15-37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>4-12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M11" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P11" t="n">
         <v>120</v>
@@ -3612,29 +3624,29 @@
         <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>41-9</t>
+          <t>41-11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12-3</t>
+          <t>12-4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>W 7</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -3650,10 +3662,10 @@
         <v>119</v>
       </c>
       <c r="P12" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -3684,22 +3696,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.65</v>
+        <v>0.659</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>34-16</t>
+          <t>36-16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3709,14 +3721,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>W 10</t>
+          <t>W 12</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -3759,17 +3771,17 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
         <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>0.588</v>
+        <v>0.598</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>29-21</t>
+          <t>31-21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3779,19 +3791,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
@@ -3800,7 +3812,7 @@
         <v>118</v>
       </c>
       <c r="P14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q14" t="n">
         <v>3</v>
@@ -3834,17 +3846,17 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
         <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.512</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>27-23</t>
+          <t>29-23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3854,19 +3866,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
@@ -3878,10 +3890,10 @@
         <v>116</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S15" t="inlineStr"/>
     </row>
@@ -3905,17 +3917,17 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>0.263</v>
+        <v>0.268</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11-39</t>
+          <t>12-40</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3925,31 +3937,31 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0-10</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L 10</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N16" t="n">
         <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P16" t="n">
         <v>126</v>
       </c>
       <c r="Q16" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R16" t="n">
         <v>15</v>
@@ -3980,36 +3992,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F17" t="n">
         <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0.638</v>
+        <v>0.646</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>31-19</t>
+          <t>33-19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>W 3</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -4024,7 +4036,7 @@
         <v>115</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
         <v>4</v>
@@ -4055,22 +4067,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>0.55</v>
+        <v>0.549</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>28-22</t>
+          <t>29-23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4084,10 +4096,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -4126,39 +4138,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>0.513</v>
+        <v>0.512</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24-26</t>
+          <t>25-27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -4173,7 +4185,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S19" t="inlineStr"/>
     </row>
@@ -4200,36 +4212,36 @@
         <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>0.463</v>
+        <v>0.451</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>24-26</t>
+          <t>24-28</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>L 3</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>27</v>
       </c>
       <c r="M20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N20" t="n">
         <v>4</v>
@@ -4241,7 +4253,7 @@
         <v>115</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R20" t="n">
         <v>10</v>
@@ -4268,22 +4280,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>0.263</v>
+        <v>0.268</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>13-37</t>
+          <t>14-38</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3-12</t>
+          <t>4-12</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4293,14 +4305,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
@@ -4343,36 +4355,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>26-24</t>
+          <t>27-25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4387,12 +4399,16 @@
         <v>116</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
         <v>6</v>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - se</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4414,17 +4430,17 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>0.55</v>
+        <v>0.549</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25-25</t>
+          <t>26-26</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -4434,16 +4450,16 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>W 4</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
@@ -4458,10 +4474,10 @@
         <v>115</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S23" t="inlineStr"/>
     </row>
@@ -4485,17 +4501,17 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G24" t="n">
-        <v>0.538</v>
+        <v>0.537</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>25-25</t>
+          <t>26-26</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -4505,16 +4521,16 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>L 1</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M24" t="n">
         <v>2</v>
@@ -4556,45 +4572,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F25" t="n">
         <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>0.513</v>
+        <v>0.524</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25-25</t>
+          <t>27-25</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8-7</t>
+          <t>10-7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>W 2</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>17</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
         <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P25" t="n">
         <v>119</v>
@@ -4630,36 +4646,36 @@
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G26" t="n">
-        <v>0.213</v>
+        <v>0.207</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11-39</t>
+          <t>11-41</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2-13</t>
+          <t>2-14</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L 8</t>
+          <t>L 10</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N26" t="n">
         <v>5</v>
@@ -4702,36 +4718,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>0.763</v>
+        <v>0.756</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>35-15</t>
+          <t>36-16</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12-3</t>
+          <t>13-3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>W 2</t>
+          <t>L 1</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4743,7 +4759,7 @@
         <v>120</v>
       </c>
       <c r="P27" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q27" t="n">
         <v>8</v>
@@ -4777,36 +4793,36 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G28" t="n">
-        <v>0.638</v>
+        <v>0.634</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>28-22</t>
+          <t>29-23</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>W 8</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M28" t="n">
         <v>10</v>
@@ -4855,14 +4871,14 @@
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G29" t="n">
-        <v>0.325</v>
+        <v>0.317</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17-33</t>
+          <t>17-34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4872,31 +4888,31 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>W 1</t>
+          <t>L 2</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>38</v>
       </c>
       <c r="M29" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N29" t="n">
         <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" t="n">
         <v>120</v>
       </c>
       <c r="Q29" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R29" t="n">
         <v>11</v>
@@ -4909,11 +4925,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Mavericks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4927,36 +4943,36 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G30" t="n">
-        <v>0.313</v>
+        <v>0.317</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19-31</t>
+          <t>14-37</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>4-12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1-9</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L 6</t>
+          <t>W 1</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M30" t="n">
         <v>36</v>
@@ -4965,13 +4981,13 @@
         <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P30" t="n">
         <v>120</v>
       </c>
       <c r="Q30" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R30" t="n">
         <v>12</v>
@@ -4984,11 +5000,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mavericks</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5005,45 +5021,45 @@
         <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G31" t="n">
-        <v>0.313</v>
+        <v>0.305</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14-36</t>
+          <t>19-33</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4-11</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>1-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L 2</t>
+          <t>L 8</t>
         </is>
       </c>
       <c r="L31" t="n">
         <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P31" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q31" t="n">
         <v>-6</v>
